--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF453BF0-B29F-4CB2-AECD-BA0CDFBC0983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B02BDE6-6245-4036-914E-678D0A6BD72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6764" uniqueCount="1472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7162" uniqueCount="1556">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -4454,6 +4454,258 @@
   </si>
   <si>
     <t>N03910178</t>
+  </si>
+  <si>
+    <t>HAMAD MOHAMMED</t>
+  </si>
+  <si>
+    <t>Co marjabi</t>
+  </si>
+  <si>
+    <t>HUUSSEIN RASHID</t>
+  </si>
+  <si>
+    <t>*8089</t>
+  </si>
+  <si>
+    <t>C/O hassan al kabsi</t>
+  </si>
+  <si>
+    <t>SAED ZAYID</t>
+  </si>
+  <si>
+    <t>20792099-</t>
+  </si>
+  <si>
+    <t>MUHAMMAD AWAIS</t>
+  </si>
+  <si>
+    <t>BB1697962</t>
+  </si>
+  <si>
+    <t>GULAWAT KHAN</t>
+  </si>
+  <si>
+    <t>KT4107105</t>
+  </si>
+  <si>
+    <t>MUHAMMAD UMAR</t>
+  </si>
+  <si>
+    <t>BH2229913</t>
+  </si>
+  <si>
+    <t>MUHAMMAD SHAHZEB</t>
+  </si>
+  <si>
+    <t>KF1344492</t>
+  </si>
+  <si>
+    <t>SABIR ALI</t>
+  </si>
+  <si>
+    <t>WT1829622</t>
+  </si>
+  <si>
+    <t>MAHMOOD IQBAL</t>
+  </si>
+  <si>
+    <t>KB1333014</t>
+  </si>
+  <si>
+    <t>C/o mh iqbal</t>
+  </si>
+  <si>
+    <t>9586 0056</t>
+  </si>
+  <si>
+    <t>MEHBOOB ALI</t>
+  </si>
+  <si>
+    <t>YG1806014</t>
+  </si>
+  <si>
+    <t>ALI AQIB</t>
+  </si>
+  <si>
+    <t>YV182581</t>
+  </si>
+  <si>
+    <t>RASHID ABDUL</t>
+  </si>
+  <si>
+    <t>AM9999334</t>
+  </si>
+  <si>
+    <t>WAJID ALI</t>
+  </si>
+  <si>
+    <t>SAMI ULLAH</t>
+  </si>
+  <si>
+    <t>WASEEM AKRAM</t>
+  </si>
+  <si>
+    <t>SAJJAD AHMED</t>
+  </si>
+  <si>
+    <t>TARIQ MAHMOOD</t>
+  </si>
+  <si>
+    <t>ASIF HUSSAIN GORAYA</t>
+  </si>
+  <si>
+    <t>JAMIL KHAN</t>
+  </si>
+  <si>
+    <t>KHAN MEHTAB</t>
+  </si>
+  <si>
+    <t>XJ4105846</t>
+  </si>
+  <si>
+    <t>ASHRAF KHAN</t>
+  </si>
+  <si>
+    <t>NA4117205</t>
+  </si>
+  <si>
+    <t>SHAHZAD CHEEMA</t>
+  </si>
+  <si>
+    <t>SHAH FAISAL</t>
+  </si>
+  <si>
+    <t>QASIM MANSOOR</t>
+  </si>
+  <si>
+    <t>MAJEED MIRZA NOMAN</t>
+  </si>
+  <si>
+    <t>BX0571943</t>
+  </si>
+  <si>
+    <t>MUNAWAR SHAMAS</t>
+  </si>
+  <si>
+    <t>HASSAIN ALI</t>
+  </si>
+  <si>
+    <t>MAHBOOB</t>
+  </si>
+  <si>
+    <t>SOHAIL RAZA</t>
+  </si>
+  <si>
+    <t>AAMIR HAYAT</t>
+  </si>
+  <si>
+    <t>WK4114895</t>
+  </si>
+  <si>
+    <t>JS1335595</t>
+  </si>
+  <si>
+    <t>ASIF RAZA</t>
+  </si>
+  <si>
+    <t>R-GEN/ASIF</t>
+  </si>
+  <si>
+    <t>TALHA</t>
+  </si>
+  <si>
+    <t>KHILAL GULAB</t>
+  </si>
+  <si>
+    <t>SAFEER HUSSAIN</t>
+  </si>
+  <si>
+    <t>LF6898235</t>
+  </si>
+  <si>
+    <t>TABASSUM HUSSSAIN</t>
+  </si>
+  <si>
+    <t>QASIM</t>
+  </si>
+  <si>
+    <t>NADDEM AHMAD</t>
+  </si>
+  <si>
+    <t>PANNA GHULAM</t>
+  </si>
+  <si>
+    <t>SUFYAN</t>
+  </si>
+  <si>
+    <t>MALIK ALLAH</t>
+  </si>
+  <si>
+    <t>NAEEM AKHTAR</t>
+  </si>
+  <si>
+    <t>239*</t>
+  </si>
+  <si>
+    <t>AFZAL HUSSAIN</t>
+  </si>
+  <si>
+    <t>ARBAZ ALI</t>
+  </si>
+  <si>
+    <t>ATIF AJMAL</t>
+  </si>
+  <si>
+    <t>MUHAMMAD KHAN</t>
+  </si>
+  <si>
+    <t>SHOAIB QAISER</t>
+  </si>
+  <si>
+    <t>2042*</t>
+  </si>
+  <si>
+    <t>ARSLAN HAIDER</t>
+  </si>
+  <si>
+    <t>RIASAT IQBAL</t>
+  </si>
+  <si>
+    <t>ADIL REHAMN</t>
+  </si>
+  <si>
+    <t>135374031*</t>
+  </si>
+  <si>
+    <t>ZAKI ULLAH</t>
+  </si>
+  <si>
+    <t>R-GEN/ISMAIL</t>
+  </si>
+  <si>
+    <t>USMAN GHANI</t>
+  </si>
+  <si>
+    <t>HABIB NOOR</t>
+  </si>
+  <si>
+    <t>9437 8226</t>
+  </si>
+  <si>
+    <t>AHMED WAQAR RIAZ</t>
+  </si>
+  <si>
+    <t>NOMAN ALI</t>
+  </si>
+  <si>
+    <t>VEER BAHADUR SINGH</t>
+  </si>
+  <si>
+    <t>Z6487688</t>
+  </si>
+  <si>
+    <t>AMIN ULLAH</t>
   </si>
 </sst>
 </file>
@@ -4680,7 +4932,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4732,6 +4984,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9CB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4808,7 +5066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5063,6 +5321,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5379,7 +5661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R890"/>
+  <dimension ref="A1:R950"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -18074,7 +18356,9 @@
       <c r="M281" s="18"/>
       <c r="N281" s="40"/>
       <c r="O281" s="51"/>
-      <c r="P281" s="18"/>
+      <c r="P281" s="86">
+        <v>46304</v>
+      </c>
       <c r="Q281" s="15">
         <v>96894693756</v>
       </c>
@@ -44034,26 +44318,24 @@
       <c r="G859" s="14">
         <v>13272</v>
       </c>
-      <c r="H859" s="15">
-        <v>98118</v>
-      </c>
+      <c r="H859" s="18"/>
       <c r="I859" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J859" s="15" t="s">
         <v>1421</v>
       </c>
-      <c r="K859" s="26" t="s">
-        <v>204</v>
+      <c r="K859" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L859" s="18"/>
       <c r="M859" s="18"/>
       <c r="N859" s="40"/>
       <c r="O859" s="51"/>
-      <c r="P859" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q859" s="18"/>
+      <c r="P859" s="18"/>
+      <c r="Q859" s="11">
+        <v>96894609416</v>
+      </c>
       <c r="R859" s="19" t="s">
         <v>11</v>
       </c>
@@ -44131,16 +44413,14 @@
       <c r="J861" s="15" t="s">
         <v>1421</v>
       </c>
-      <c r="K861" s="26" t="s">
-        <v>204</v>
+      <c r="K861" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L861" s="18"/>
       <c r="M861" s="18"/>
       <c r="N861" s="40"/>
       <c r="O861" s="51"/>
-      <c r="P861" s="28" t="s">
-        <v>318</v>
-      </c>
+      <c r="P861" s="18"/>
       <c r="Q861" s="18"/>
       <c r="R861" s="19" t="s">
         <v>11</v>
@@ -45436,6 +45716,2638 @@
         <v>14</v>
       </c>
     </row>
+    <row r="891" spans="1:18" ht="15" thickBot="1">
+      <c r="A891" s="45">
+        <v>1</v>
+      </c>
+      <c r="B891" s="87">
+        <v>46270</v>
+      </c>
+      <c r="C891" s="68" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D891" s="68">
+        <v>2400218</v>
+      </c>
+      <c r="E891" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="F891" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="G891" s="48">
+        <v>267</v>
+      </c>
+      <c r="H891" s="49">
+        <v>6793</v>
+      </c>
+      <c r="I891" s="84" t="s">
+        <v>10</v>
+      </c>
+      <c r="J891" s="49" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K891" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="L891" s="50"/>
+      <c r="M891" s="50"/>
+      <c r="N891" s="50"/>
+      <c r="O891" s="50"/>
+      <c r="P891" s="89" t="s">
+        <v>1473</v>
+      </c>
+      <c r="Q891" s="50"/>
+      <c r="R891" s="90" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="892" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A892" s="2">
+        <v>2</v>
+      </c>
+      <c r="B892" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C892" s="11" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D892" s="11">
+        <v>18762555</v>
+      </c>
+      <c r="E892" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F892" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G892" s="14" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H892" s="15">
+        <v>5193</v>
+      </c>
+      <c r="I892" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J892" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K892" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L892" s="18"/>
+      <c r="M892" s="18"/>
+      <c r="N892" s="40"/>
+      <c r="O892" s="51"/>
+      <c r="P892" s="28" t="s">
+        <v>1476</v>
+      </c>
+      <c r="Q892" s="18"/>
+      <c r="R892" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="893" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A893" s="2">
+        <v>3</v>
+      </c>
+      <c r="B893" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C893" s="11" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D893" s="91" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E893" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F893" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G893" s="14">
+        <v>3604</v>
+      </c>
+      <c r="H893" s="15">
+        <v>7191</v>
+      </c>
+      <c r="I893" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J893" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K893" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L893" s="18"/>
+      <c r="M893" s="18"/>
+      <c r="N893" s="40"/>
+      <c r="O893" s="51"/>
+      <c r="P893" s="28" t="s">
+        <v>1476</v>
+      </c>
+      <c r="Q893" s="18"/>
+      <c r="R893" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="894" spans="1:18" ht="15" thickBot="1">
+      <c r="A894" s="2">
+        <v>4</v>
+      </c>
+      <c r="B894" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C894" s="11" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D894" s="11" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E894" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F894" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G894" s="14">
+        <v>70020</v>
+      </c>
+      <c r="H894" s="15">
+        <v>64726</v>
+      </c>
+      <c r="I894" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J894" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K894" s="18"/>
+      <c r="L894" s="18"/>
+      <c r="M894" s="18"/>
+      <c r="N894" s="40"/>
+      <c r="O894" s="51"/>
+      <c r="P894" s="18"/>
+      <c r="Q894" s="15">
+        <v>76753817</v>
+      </c>
+      <c r="R894" s="18"/>
+    </row>
+    <row r="895" spans="1:18" ht="15" thickBot="1">
+      <c r="A895" s="2">
+        <v>5</v>
+      </c>
+      <c r="B895" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C895" s="11" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D895" s="11" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E895" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F895" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G895" s="14">
+        <v>25549</v>
+      </c>
+      <c r="H895" s="18"/>
+      <c r="I895" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J895" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K895" s="18"/>
+      <c r="L895" s="18"/>
+      <c r="M895" s="18"/>
+      <c r="N895" s="40"/>
+      <c r="O895" s="51"/>
+      <c r="P895" s="18"/>
+      <c r="Q895" s="15">
+        <v>559077873</v>
+      </c>
+      <c r="R895" s="18"/>
+    </row>
+    <row r="896" spans="1:18" ht="15" thickBot="1">
+      <c r="A896" s="2">
+        <v>6</v>
+      </c>
+      <c r="B896" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C896" s="11" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D896" s="11" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E896" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F896" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G896" s="14">
+        <v>50456</v>
+      </c>
+      <c r="H896" s="15">
+        <v>41059</v>
+      </c>
+      <c r="I896" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J896" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K896" s="18"/>
+      <c r="L896" s="18"/>
+      <c r="M896" s="18"/>
+      <c r="N896" s="40"/>
+      <c r="O896" s="51"/>
+      <c r="P896" s="18"/>
+      <c r="Q896" s="15">
+        <v>582797351</v>
+      </c>
+      <c r="R896" s="18"/>
+    </row>
+    <row r="897" spans="1:18" ht="23.4" thickBot="1">
+      <c r="A897" s="2">
+        <v>7</v>
+      </c>
+      <c r="B897" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C897" s="11" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D897" s="11" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E897" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F897" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G897" s="14">
+        <v>50438</v>
+      </c>
+      <c r="H897" s="15">
+        <v>24193</v>
+      </c>
+      <c r="I897" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J897" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K897" s="18"/>
+      <c r="L897" s="18"/>
+      <c r="M897" s="18"/>
+      <c r="N897" s="40"/>
+      <c r="O897" s="51"/>
+      <c r="P897" s="18"/>
+      <c r="Q897" s="15">
+        <v>95881784</v>
+      </c>
+      <c r="R897" s="18"/>
+    </row>
+    <row r="898" spans="1:18" ht="15" thickBot="1">
+      <c r="A898" s="2">
+        <v>8</v>
+      </c>
+      <c r="B898" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C898" s="11" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D898" s="11" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E898" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F898" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G898" s="14">
+        <v>41738</v>
+      </c>
+      <c r="H898" s="15">
+        <v>19723</v>
+      </c>
+      <c r="I898" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J898" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K898" s="18"/>
+      <c r="L898" s="18"/>
+      <c r="M898" s="18"/>
+      <c r="N898" s="40"/>
+      <c r="O898" s="51"/>
+      <c r="P898" s="18"/>
+      <c r="Q898" s="15">
+        <v>96027432</v>
+      </c>
+      <c r="R898" s="18"/>
+    </row>
+    <row r="899" spans="1:18" ht="15" thickBot="1">
+      <c r="A899" s="2">
+        <v>9</v>
+      </c>
+      <c r="B899" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C899" s="11" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D899" s="11" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E899" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F899" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G899" s="14">
+        <v>84837</v>
+      </c>
+      <c r="H899" s="15">
+        <v>84470</v>
+      </c>
+      <c r="I899" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J899" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K899" s="18"/>
+      <c r="L899" s="18"/>
+      <c r="M899" s="18"/>
+      <c r="N899" s="40"/>
+      <c r="O899" s="51"/>
+      <c r="P899" s="28" t="s">
+        <v>1491</v>
+      </c>
+      <c r="Q899" s="15" t="s">
+        <v>1492</v>
+      </c>
+      <c r="R899" s="18"/>
+    </row>
+    <row r="900" spans="1:18" ht="15" thickBot="1">
+      <c r="A900" s="2">
+        <v>10</v>
+      </c>
+      <c r="B900" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C900" s="11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D900" s="11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E900" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F900" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G900" s="14">
+        <v>31204</v>
+      </c>
+      <c r="H900" s="15">
+        <v>43596</v>
+      </c>
+      <c r="I900" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J900" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K900" s="18"/>
+      <c r="L900" s="18"/>
+      <c r="M900" s="18"/>
+      <c r="N900" s="40"/>
+      <c r="O900" s="51"/>
+      <c r="P900" s="18"/>
+      <c r="Q900" s="15">
+        <v>94183407</v>
+      </c>
+      <c r="R900" s="18"/>
+    </row>
+    <row r="901" spans="1:18" ht="15" thickBot="1">
+      <c r="A901" s="2">
+        <v>11</v>
+      </c>
+      <c r="B901" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C901" s="11" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D901" s="11" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E901" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F901" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G901" s="14">
+        <v>54939</v>
+      </c>
+      <c r="H901" s="15">
+        <v>47670</v>
+      </c>
+      <c r="I901" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J901" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K901" s="18"/>
+      <c r="L901" s="18"/>
+      <c r="M901" s="18"/>
+      <c r="N901" s="40"/>
+      <c r="O901" s="51"/>
+      <c r="P901" s="18"/>
+      <c r="Q901" s="15">
+        <v>96896036588</v>
+      </c>
+      <c r="R901" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="902" spans="1:18" ht="15" thickBot="1">
+      <c r="A902" s="2">
+        <v>12</v>
+      </c>
+      <c r="B902" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C902" s="11" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D902" s="11" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E902" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F902" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G902" s="14">
+        <v>64049</v>
+      </c>
+      <c r="H902" s="15">
+        <v>20257</v>
+      </c>
+      <c r="I902" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J902" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K902" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="L902" s="18"/>
+      <c r="M902" s="18"/>
+      <c r="N902" s="40"/>
+      <c r="O902" s="51"/>
+      <c r="P902" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q902" s="18"/>
+      <c r="R902" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="903" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A903" s="2">
+        <v>13</v>
+      </c>
+      <c r="B903" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C903" s="11" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D903" s="11">
+        <v>124874423</v>
+      </c>
+      <c r="E903" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F903" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G903" s="14">
+        <v>4748</v>
+      </c>
+      <c r="H903" s="15">
+        <v>8662</v>
+      </c>
+      <c r="I903" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J903" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K903" s="18"/>
+      <c r="L903" s="18"/>
+      <c r="M903" s="18"/>
+      <c r="N903" s="40"/>
+      <c r="O903" s="51"/>
+      <c r="P903" s="18"/>
+      <c r="Q903" s="18"/>
+      <c r="R903" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="904" spans="1:18" ht="15" thickBot="1">
+      <c r="A904" s="2">
+        <v>14</v>
+      </c>
+      <c r="B904" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C904" s="11" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D904" s="11">
+        <v>118309176</v>
+      </c>
+      <c r="E904" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F904" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G904" s="14">
+        <v>9795</v>
+      </c>
+      <c r="H904" s="15">
+        <v>-3790</v>
+      </c>
+      <c r="I904" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J904" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K904" s="18"/>
+      <c r="L904" s="18"/>
+      <c r="M904" s="18"/>
+      <c r="N904" s="40"/>
+      <c r="O904" s="51"/>
+      <c r="P904" s="18"/>
+      <c r="Q904" s="15">
+        <v>94676174</v>
+      </c>
+      <c r="R904" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="905" spans="1:18" ht="15" thickBot="1">
+      <c r="A905" s="2">
+        <v>15</v>
+      </c>
+      <c r="B905" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C905" s="11" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D905" s="11">
+        <v>94006643</v>
+      </c>
+      <c r="E905" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F905" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G905" s="14">
+        <v>906</v>
+      </c>
+      <c r="H905" s="15">
+        <v>1029</v>
+      </c>
+      <c r="I905" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J905" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K905" s="18"/>
+      <c r="L905" s="18"/>
+      <c r="M905" s="18"/>
+      <c r="N905" s="40"/>
+      <c r="O905" s="51"/>
+      <c r="P905" s="18"/>
+      <c r="Q905" s="15">
+        <v>94535329</v>
+      </c>
+      <c r="R905" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="906" spans="1:18" ht="15" thickBot="1">
+      <c r="A906" s="2">
+        <v>16</v>
+      </c>
+      <c r="B906" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C906" s="11" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D906" s="11">
+        <v>126179269</v>
+      </c>
+      <c r="E906" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F906" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G906" s="14">
+        <v>7888</v>
+      </c>
+      <c r="H906" s="15">
+        <v>5504</v>
+      </c>
+      <c r="I906" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J906" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K906" s="18"/>
+      <c r="L906" s="18"/>
+      <c r="M906" s="18"/>
+      <c r="N906" s="40"/>
+      <c r="O906" s="51"/>
+      <c r="P906" s="18"/>
+      <c r="Q906" s="15">
+        <v>96896949016</v>
+      </c>
+      <c r="R906" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="907" spans="1:18" ht="15" thickBot="1">
+      <c r="A907" s="2">
+        <v>17</v>
+      </c>
+      <c r="B907" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C907" s="11" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D907" s="11">
+        <v>137716041</v>
+      </c>
+      <c r="E907" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F907" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G907" s="14">
+        <v>3228</v>
+      </c>
+      <c r="H907" s="15">
+        <v>-4523</v>
+      </c>
+      <c r="I907" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J907" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K907" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L907" s="18"/>
+      <c r="M907" s="18"/>
+      <c r="N907" s="40"/>
+      <c r="O907" s="51"/>
+      <c r="P907" s="18"/>
+      <c r="Q907" s="18"/>
+      <c r="R907" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="908" spans="1:18" ht="23.4" thickBot="1">
+      <c r="A908" s="2">
+        <v>18</v>
+      </c>
+      <c r="B908" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C908" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D908" s="11">
+        <v>102033848</v>
+      </c>
+      <c r="E908" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F908" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G908" s="14">
+        <v>8850</v>
+      </c>
+      <c r="H908" s="15">
+        <v>239</v>
+      </c>
+      <c r="I908" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J908" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K908" s="18"/>
+      <c r="L908" s="18"/>
+      <c r="M908" s="18"/>
+      <c r="N908" s="40"/>
+      <c r="O908" s="51"/>
+      <c r="P908" s="18"/>
+      <c r="Q908" s="15">
+        <v>94709965</v>
+      </c>
+      <c r="R908" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="909" spans="1:18" ht="15" thickBot="1">
+      <c r="A909" s="2">
+        <v>19</v>
+      </c>
+      <c r="B909" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C909" s="11" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D909" s="11">
+        <v>90039233</v>
+      </c>
+      <c r="E909" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F909" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G909" s="14">
+        <v>4467</v>
+      </c>
+      <c r="H909" s="15">
+        <v>2766</v>
+      </c>
+      <c r="I909" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J909" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K909" s="18"/>
+      <c r="L909" s="18"/>
+      <c r="M909" s="18"/>
+      <c r="N909" s="40"/>
+      <c r="O909" s="51"/>
+      <c r="P909" s="18"/>
+      <c r="Q909" s="15">
+        <v>94247434</v>
+      </c>
+      <c r="R909" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="910" spans="1:18" ht="15" thickBot="1">
+      <c r="A910" s="2">
+        <v>20</v>
+      </c>
+      <c r="B910" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C910" s="11" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D910" s="11" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E910" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F910" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G910" s="14">
+        <v>71968</v>
+      </c>
+      <c r="H910" s="15">
+        <v>13188</v>
+      </c>
+      <c r="I910" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J910" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K910" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L910" s="18"/>
+      <c r="M910" s="18"/>
+      <c r="N910" s="40"/>
+      <c r="O910" s="51"/>
+      <c r="P910" s="18"/>
+      <c r="Q910" s="18"/>
+      <c r="R910" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="911" spans="1:18" ht="15" thickBot="1">
+      <c r="A911" s="2">
+        <v>21</v>
+      </c>
+      <c r="B911" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C911" s="11" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D911" s="11" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E911" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F911" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G911" s="14">
+        <v>88392</v>
+      </c>
+      <c r="H911" s="15">
+        <v>6438</v>
+      </c>
+      <c r="I911" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J911" s="15" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K911" s="18"/>
+      <c r="L911" s="18"/>
+      <c r="M911" s="18"/>
+      <c r="N911" s="40"/>
+      <c r="O911" s="51"/>
+      <c r="P911" s="18"/>
+      <c r="Q911" s="15">
+        <v>96268855</v>
+      </c>
+      <c r="R911" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="912" spans="1:18" ht="15" thickBot="1">
+      <c r="A912" s="2">
+        <v>22</v>
+      </c>
+      <c r="B912" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C912" s="11" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D912" s="11">
+        <v>102315974</v>
+      </c>
+      <c r="E912" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F912" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G912" s="14">
+        <v>3633</v>
+      </c>
+      <c r="H912" s="15">
+        <v>4668</v>
+      </c>
+      <c r="I912" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J912" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K912" s="18"/>
+      <c r="L912" s="18"/>
+      <c r="M912" s="18"/>
+      <c r="N912" s="40"/>
+      <c r="O912" s="51"/>
+      <c r="P912" s="18"/>
+      <c r="Q912" s="15">
+        <v>96257805</v>
+      </c>
+      <c r="R912" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="913" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A913" s="2">
+        <v>23</v>
+      </c>
+      <c r="B913" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C913" s="11" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D913" s="11">
+        <v>69523302</v>
+      </c>
+      <c r="E913" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F913" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G913" s="14">
+        <v>-2317</v>
+      </c>
+      <c r="H913" s="15">
+        <v>8695</v>
+      </c>
+      <c r="I913" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J913" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="K913" s="18"/>
+      <c r="L913" s="18"/>
+      <c r="M913" s="18"/>
+      <c r="N913" s="40"/>
+      <c r="O913" s="51"/>
+      <c r="P913" s="18"/>
+      <c r="Q913" s="15">
+        <v>92518156</v>
+      </c>
+      <c r="R913" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="914" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A914" s="2">
+        <v>24</v>
+      </c>
+      <c r="B914" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C914" s="11" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D914" s="11">
+        <v>125431335</v>
+      </c>
+      <c r="E914" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F914" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G914" s="14">
+        <v>4288</v>
+      </c>
+      <c r="H914" s="15">
+        <v>7624</v>
+      </c>
+      <c r="I914" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J914" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="K914" s="18"/>
+      <c r="L914" s="18"/>
+      <c r="M914" s="18"/>
+      <c r="N914" s="40"/>
+      <c r="O914" s="51"/>
+      <c r="P914" s="18"/>
+      <c r="Q914" s="15">
+        <v>94176472</v>
+      </c>
+      <c r="R914" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="915" spans="1:18" ht="23.4" thickBot="1">
+      <c r="A915" s="2">
+        <v>25</v>
+      </c>
+      <c r="B915" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C915" s="11" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D915" s="11" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E915" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F915" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G915" s="14">
+        <v>5266</v>
+      </c>
+      <c r="H915" s="15">
+        <v>27492</v>
+      </c>
+      <c r="I915" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J915" s="15" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K915" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="L915" s="18"/>
+      <c r="M915" s="18"/>
+      <c r="N915" s="40"/>
+      <c r="O915" s="51"/>
+      <c r="P915" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q915" s="18"/>
+      <c r="R915" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="916" spans="1:18" ht="15" thickBot="1">
+      <c r="A916" s="2">
+        <v>26</v>
+      </c>
+      <c r="B916" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C916" s="11" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D916" s="11">
+        <v>137764894</v>
+      </c>
+      <c r="E916" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F916" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G916" s="14">
+        <v>7086</v>
+      </c>
+      <c r="H916" s="15">
+        <v>7270</v>
+      </c>
+      <c r="I916" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J916" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K916" s="18"/>
+      <c r="L916" s="18"/>
+      <c r="M916" s="18"/>
+      <c r="N916" s="40"/>
+      <c r="O916" s="51"/>
+      <c r="P916" s="18"/>
+      <c r="Q916" s="18"/>
+      <c r="R916" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="917" spans="1:18" ht="15" thickBot="1">
+      <c r="A917" s="2">
+        <v>27</v>
+      </c>
+      <c r="B917" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C917" s="11" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D917" s="11">
+        <v>119176321</v>
+      </c>
+      <c r="E917" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F917" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G917" s="14">
+        <v>4551</v>
+      </c>
+      <c r="H917" s="15">
+        <v>-4179</v>
+      </c>
+      <c r="I917" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J917" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K917" s="18"/>
+      <c r="L917" s="18"/>
+      <c r="M917" s="18"/>
+      <c r="N917" s="40"/>
+      <c r="O917" s="51"/>
+      <c r="P917" s="18"/>
+      <c r="Q917" s="15">
+        <v>96963610</v>
+      </c>
+      <c r="R917" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="918" spans="1:18" ht="15" thickBot="1">
+      <c r="A918" s="2">
+        <v>28</v>
+      </c>
+      <c r="B918" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C918" s="11" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D918" s="11">
+        <v>114035286</v>
+      </c>
+      <c r="E918" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F918" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G918" s="14">
+        <v>1958</v>
+      </c>
+      <c r="H918" s="15">
+        <v>8223</v>
+      </c>
+      <c r="I918" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J918" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K918" s="18"/>
+      <c r="L918" s="18"/>
+      <c r="M918" s="18"/>
+      <c r="N918" s="40"/>
+      <c r="O918" s="51"/>
+      <c r="P918" s="18"/>
+      <c r="Q918" s="15">
+        <v>94163992</v>
+      </c>
+      <c r="R918" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="919" spans="1:18" ht="15" thickBot="1">
+      <c r="A919" s="2">
+        <v>29</v>
+      </c>
+      <c r="B919" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C919" s="11" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D919" s="11">
+        <v>113258018</v>
+      </c>
+      <c r="E919" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F919" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G919" s="14">
+        <v>7045</v>
+      </c>
+      <c r="H919" s="15">
+        <v>3526</v>
+      </c>
+      <c r="I919" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J919" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K919" s="18"/>
+      <c r="L919" s="18"/>
+      <c r="M919" s="18"/>
+      <c r="N919" s="40"/>
+      <c r="O919" s="51"/>
+      <c r="P919" s="18"/>
+      <c r="Q919" s="15">
+        <v>97103027</v>
+      </c>
+      <c r="R919" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="920" spans="1:18" ht="42" thickBot="1">
+      <c r="A920" s="2">
+        <v>30</v>
+      </c>
+      <c r="B920" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C920" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D920" s="11" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E920" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F920" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G920" s="14">
+        <v>34251</v>
+      </c>
+      <c r="H920" s="15">
+        <v>35216</v>
+      </c>
+      <c r="I920" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J920" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="K920" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L920" s="18"/>
+      <c r="M920" s="18"/>
+      <c r="N920" s="40"/>
+      <c r="O920" s="51"/>
+      <c r="P920" s="18"/>
+      <c r="Q920" s="44">
+        <v>509963565</v>
+      </c>
+      <c r="R920" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="921" spans="1:18" ht="42" thickBot="1">
+      <c r="A921" s="2">
+        <v>31</v>
+      </c>
+      <c r="B921" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C921" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D921" s="11" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E921" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F921" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G921" s="14">
+        <v>14608</v>
+      </c>
+      <c r="H921" s="15">
+        <v>94390</v>
+      </c>
+      <c r="I921" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J921" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="K921" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L921" s="18"/>
+      <c r="M921" s="18"/>
+      <c r="N921" s="40"/>
+      <c r="O921" s="51"/>
+      <c r="P921" s="18"/>
+      <c r="Q921" s="38">
+        <v>569146906</v>
+      </c>
+      <c r="R921" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="922" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A922" s="2">
+        <v>32</v>
+      </c>
+      <c r="B922" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C922" s="11" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D922" s="11">
+        <v>79806894</v>
+      </c>
+      <c r="E922" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F922" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G922" s="14">
+        <v>4818</v>
+      </c>
+      <c r="H922" s="15">
+        <v>8451</v>
+      </c>
+      <c r="I922" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J922" s="15" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K922" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L922" s="18"/>
+      <c r="M922" s="18"/>
+      <c r="N922" s="40"/>
+      <c r="O922" s="51"/>
+      <c r="P922" s="18"/>
+      <c r="Q922" s="38">
+        <v>92622403</v>
+      </c>
+      <c r="R922" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="923" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A923" s="2">
+        <v>33</v>
+      </c>
+      <c r="B923" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C923" s="11" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D923" s="11">
+        <v>1268553320</v>
+      </c>
+      <c r="E923" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F923" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G923" s="14">
+        <v>5495</v>
+      </c>
+      <c r="H923" s="15">
+        <v>5825</v>
+      </c>
+      <c r="I923" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J923" s="15" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K923" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L923" s="18"/>
+      <c r="M923" s="18"/>
+      <c r="N923" s="40"/>
+      <c r="O923" s="51"/>
+      <c r="P923" s="18"/>
+      <c r="Q923" s="38">
+        <v>90281786</v>
+      </c>
+      <c r="R923" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="924" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A924" s="2">
+        <v>34</v>
+      </c>
+      <c r="B924" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C924" s="11" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D924" s="11">
+        <v>84388626</v>
+      </c>
+      <c r="E924" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F924" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G924" s="14">
+        <v>7756</v>
+      </c>
+      <c r="H924" s="15">
+        <v>5952</v>
+      </c>
+      <c r="I924" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J924" s="15" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K924" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L924" s="18"/>
+      <c r="M924" s="18"/>
+      <c r="N924" s="40"/>
+      <c r="O924" s="51"/>
+      <c r="P924" s="18"/>
+      <c r="Q924" s="38">
+        <v>97046988</v>
+      </c>
+      <c r="R924" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="925" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A925" s="2">
+        <v>35</v>
+      </c>
+      <c r="B925" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C925" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="D925" s="11">
+        <v>60684218</v>
+      </c>
+      <c r="E925" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F925" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G925" s="14">
+        <v>5814</v>
+      </c>
+      <c r="H925" s="15">
+        <v>8864</v>
+      </c>
+      <c r="I925" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J925" s="15" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K925" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L925" s="18"/>
+      <c r="M925" s="18"/>
+      <c r="N925" s="40"/>
+      <c r="O925" s="51"/>
+      <c r="P925" s="18"/>
+      <c r="Q925" s="38">
+        <v>79896803</v>
+      </c>
+      <c r="R925" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="926" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A926" s="2">
+        <v>36</v>
+      </c>
+      <c r="B926" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C926" s="11" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D926" s="11" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E926" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F926" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G926" s="14">
+        <v>51939</v>
+      </c>
+      <c r="H926" s="15">
+        <v>90020</v>
+      </c>
+      <c r="I926" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J926" s="15" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K926" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L926" s="18"/>
+      <c r="M926" s="18"/>
+      <c r="N926" s="40"/>
+      <c r="O926" s="51"/>
+      <c r="P926" s="18"/>
+      <c r="Q926" s="44">
+        <v>76658220</v>
+      </c>
+      <c r="R926" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="927" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A927" s="2">
+        <v>37</v>
+      </c>
+      <c r="B927" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C927" s="11" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D927" s="11">
+        <v>93734919</v>
+      </c>
+      <c r="E927" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F927" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G927" s="14">
+        <v>4938</v>
+      </c>
+      <c r="H927" s="15">
+        <v>7490</v>
+      </c>
+      <c r="I927" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J927" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K927" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L927" s="18"/>
+      <c r="M927" s="18"/>
+      <c r="N927" s="40"/>
+      <c r="O927" s="51"/>
+      <c r="P927" s="18"/>
+      <c r="Q927" s="18"/>
+      <c r="R927" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="928" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A928" s="2">
+        <v>38</v>
+      </c>
+      <c r="B928" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C928" s="11" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D928" s="11">
+        <v>91031583</v>
+      </c>
+      <c r="E928" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F928" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G928" s="14">
+        <v>1657</v>
+      </c>
+      <c r="H928" s="15">
+        <v>9012</v>
+      </c>
+      <c r="I928" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J928" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K928" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L928" s="18"/>
+      <c r="M928" s="18"/>
+      <c r="N928" s="40"/>
+      <c r="O928" s="51"/>
+      <c r="P928" s="18"/>
+      <c r="Q928" s="18"/>
+      <c r="R928" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="929" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A929" s="2">
+        <v>39</v>
+      </c>
+      <c r="B929" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C929" s="11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D929" s="11">
+        <v>124463956</v>
+      </c>
+      <c r="E929" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F929" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G929" s="14">
+        <v>1338</v>
+      </c>
+      <c r="H929" s="15">
+        <v>2005</v>
+      </c>
+      <c r="I929" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J929" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K929" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L929" s="18"/>
+      <c r="M929" s="18"/>
+      <c r="N929" s="40"/>
+      <c r="O929" s="51"/>
+      <c r="P929" s="18"/>
+      <c r="Q929" s="18"/>
+      <c r="R929" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="930" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A930" s="2">
+        <v>40</v>
+      </c>
+      <c r="B930" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C930" s="11" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D930" s="11">
+        <v>104757471</v>
+      </c>
+      <c r="E930" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F930" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G930" s="14">
+        <v>4583</v>
+      </c>
+      <c r="H930" s="15">
+        <v>8485</v>
+      </c>
+      <c r="I930" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J930" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K930" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L930" s="18"/>
+      <c r="M930" s="18"/>
+      <c r="N930" s="40"/>
+      <c r="O930" s="51"/>
+      <c r="P930" s="18"/>
+      <c r="Q930" s="18"/>
+      <c r="R930" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="931" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A931" s="2">
+        <v>41</v>
+      </c>
+      <c r="B931" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C931" s="11" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D931" s="11">
+        <v>131268366</v>
+      </c>
+      <c r="E931" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F931" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G931" s="14">
+        <v>6030</v>
+      </c>
+      <c r="H931" s="15">
+        <v>6055</v>
+      </c>
+      <c r="I931" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J931" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K931" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L931" s="18"/>
+      <c r="M931" s="18"/>
+      <c r="N931" s="40"/>
+      <c r="O931" s="51"/>
+      <c r="P931" s="18"/>
+      <c r="Q931" s="18"/>
+      <c r="R931" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="932" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A932" s="2">
+        <v>42</v>
+      </c>
+      <c r="B932" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C932" s="11" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D932" s="11">
+        <v>77256127</v>
+      </c>
+      <c r="E932" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F932" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G932" s="14">
+        <v>6948</v>
+      </c>
+      <c r="H932" s="15">
+        <v>3985</v>
+      </c>
+      <c r="I932" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J932" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K932" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L932" s="18"/>
+      <c r="M932" s="18"/>
+      <c r="N932" s="40"/>
+      <c r="O932" s="51"/>
+      <c r="P932" s="18"/>
+      <c r="Q932" s="22">
+        <v>98511756</v>
+      </c>
+      <c r="R932" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="933" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A933" s="2">
+        <v>43</v>
+      </c>
+      <c r="B933" s="57">
+        <v>46270</v>
+      </c>
+      <c r="C933" s="11" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D933" s="11">
+        <v>109950298</v>
+      </c>
+      <c r="E933" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F933" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G933" s="14">
+        <v>4139</v>
+      </c>
+      <c r="H933" s="15" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I933" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J933" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K933" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L933" s="18"/>
+      <c r="M933" s="18"/>
+      <c r="N933" s="40"/>
+      <c r="O933" s="51"/>
+      <c r="P933" s="18"/>
+      <c r="Q933" s="44">
+        <v>98279636</v>
+      </c>
+      <c r="R933" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="934" spans="1:18" ht="15" thickBot="1">
+      <c r="A934" s="45">
+        <v>1</v>
+      </c>
+      <c r="B934" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C934" s="68" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D934" s="68">
+        <v>76988431</v>
+      </c>
+      <c r="E934" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F934" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G934" s="48">
+        <v>4739</v>
+      </c>
+      <c r="H934" s="49">
+        <v>4881</v>
+      </c>
+      <c r="I934" s="92" t="s">
+        <v>107</v>
+      </c>
+      <c r="J934" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="K934" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="L934" s="93">
+        <v>94660026</v>
+      </c>
+      <c r="M934" s="50"/>
+      <c r="N934" s="50"/>
+      <c r="O934" s="50"/>
+      <c r="P934" s="50"/>
+      <c r="Q934" s="50"/>
+      <c r="R934" s="50"/>
+    </row>
+    <row r="935" spans="1:18" ht="15" thickBot="1">
+      <c r="A935" s="45">
+        <v>2</v>
+      </c>
+      <c r="B935" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C935" s="11" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D935" s="11">
+        <v>13122821</v>
+      </c>
+      <c r="E935" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F935" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G935" s="14">
+        <v>419</v>
+      </c>
+      <c r="H935" s="15">
+        <v>153</v>
+      </c>
+      <c r="I935" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J935" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="K935" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L935" s="22">
+        <v>95870014</v>
+      </c>
+      <c r="M935" s="18"/>
+      <c r="N935" s="40"/>
+      <c r="O935" s="51"/>
+      <c r="P935" s="18"/>
+      <c r="Q935" s="18"/>
+      <c r="R935" s="18"/>
+    </row>
+    <row r="936" spans="1:18" ht="15" thickBot="1">
+      <c r="A936" s="45">
+        <v>3</v>
+      </c>
+      <c r="B936" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C936" s="11" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D936" s="11">
+        <v>102867633</v>
+      </c>
+      <c r="E936" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F936" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G936" s="14">
+        <v>7623</v>
+      </c>
+      <c r="H936" s="15">
+        <v>6997</v>
+      </c>
+      <c r="I936" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J936" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="K936" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L936" s="22">
+        <v>91322615</v>
+      </c>
+      <c r="M936" s="18"/>
+      <c r="N936" s="40"/>
+      <c r="O936" s="51"/>
+      <c r="P936" s="18"/>
+      <c r="Q936" s="18"/>
+      <c r="R936" s="18"/>
+    </row>
+    <row r="937" spans="1:18" ht="15" thickBot="1">
+      <c r="A937" s="45">
+        <v>4</v>
+      </c>
+      <c r="B937" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C937" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D937" s="11">
+        <v>93304638</v>
+      </c>
+      <c r="E937" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F937" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G937" s="14">
+        <v>155</v>
+      </c>
+      <c r="H937" s="15">
+        <v>5782</v>
+      </c>
+      <c r="I937" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J937" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="K937" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L937" s="22">
+        <v>94319762</v>
+      </c>
+      <c r="M937" s="18"/>
+      <c r="N937" s="40"/>
+      <c r="O937" s="51"/>
+      <c r="P937" s="18"/>
+      <c r="Q937" s="18"/>
+      <c r="R937" s="18"/>
+    </row>
+    <row r="938" spans="1:18" ht="15" thickBot="1">
+      <c r="A938" s="45">
+        <v>5</v>
+      </c>
+      <c r="B938" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C938" s="11" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D938" s="11">
+        <v>133275068</v>
+      </c>
+      <c r="E938" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F938" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G938" s="14">
+        <v>9302</v>
+      </c>
+      <c r="H938" s="15">
+        <v>1400</v>
+      </c>
+      <c r="I938" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J938" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="K938" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L938" s="22">
+        <v>97617271</v>
+      </c>
+      <c r="M938" s="18"/>
+      <c r="N938" s="40"/>
+      <c r="O938" s="51"/>
+      <c r="P938" s="18"/>
+      <c r="Q938" s="18"/>
+      <c r="R938" s="18"/>
+    </row>
+    <row r="939" spans="1:18" ht="15" thickBot="1">
+      <c r="A939" s="45">
+        <v>6</v>
+      </c>
+      <c r="B939" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C939" s="11" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D939" s="11">
+        <v>124280971</v>
+      </c>
+      <c r="E939" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F939" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G939" s="14" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H939" s="15">
+        <v>4932</v>
+      </c>
+      <c r="I939" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J939" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="K939" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L939" s="22">
+        <v>95068978</v>
+      </c>
+      <c r="M939" s="18"/>
+      <c r="N939" s="40"/>
+      <c r="O939" s="51"/>
+      <c r="P939" s="18"/>
+      <c r="Q939" s="18"/>
+      <c r="R939" s="18"/>
+    </row>
+    <row r="940" spans="1:18" ht="15" thickBot="1">
+      <c r="A940" s="45">
+        <v>7</v>
+      </c>
+      <c r="B940" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C940" s="11" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D940" s="11">
+        <v>129241576</v>
+      </c>
+      <c r="E940" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F940" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G940" s="14">
+        <v>6937</v>
+      </c>
+      <c r="H940" s="15">
+        <v>3700</v>
+      </c>
+      <c r="I940" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J940" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="K940" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L940" s="18"/>
+      <c r="M940" s="18"/>
+      <c r="N940" s="40"/>
+      <c r="O940" s="51"/>
+      <c r="P940" s="18"/>
+      <c r="Q940" s="18"/>
+      <c r="R940" s="18"/>
+    </row>
+    <row r="941" spans="1:18" ht="15" thickBot="1">
+      <c r="A941" s="45">
+        <v>8</v>
+      </c>
+      <c r="B941" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C941" s="11" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D941" s="11">
+        <v>96801698</v>
+      </c>
+      <c r="E941" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F941" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G941" s="14">
+        <v>7327</v>
+      </c>
+      <c r="H941" s="15">
+        <v>6326</v>
+      </c>
+      <c r="I941" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J941" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="K941" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L941" s="18"/>
+      <c r="M941" s="18"/>
+      <c r="N941" s="40"/>
+      <c r="O941" s="51"/>
+      <c r="P941" s="18"/>
+      <c r="Q941" s="18"/>
+      <c r="R941" s="18"/>
+    </row>
+    <row r="942" spans="1:18" ht="15" thickBot="1">
+      <c r="A942" s="45">
+        <v>9</v>
+      </c>
+      <c r="B942" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C942" s="11" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D942" s="11">
+        <v>123546555</v>
+      </c>
+      <c r="E942" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F942" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G942" s="14">
+        <v>626</v>
+      </c>
+      <c r="H942" s="15">
+        <v>7743</v>
+      </c>
+      <c r="I942" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J942" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="K942" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L942" s="18"/>
+      <c r="M942" s="18"/>
+      <c r="N942" s="40"/>
+      <c r="O942" s="51"/>
+      <c r="P942" s="18"/>
+      <c r="Q942" s="18"/>
+      <c r="R942" s="18"/>
+    </row>
+    <row r="943" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A943" s="45">
+        <v>10</v>
+      </c>
+      <c r="B943" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C943" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D943" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E943" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F943" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G943" s="14">
+        <v>7990</v>
+      </c>
+      <c r="H943" s="15">
+        <v>3252</v>
+      </c>
+      <c r="I943" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J943" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K943" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L943" s="18"/>
+      <c r="M943" s="18"/>
+      <c r="N943" s="40"/>
+      <c r="O943" s="51"/>
+      <c r="P943" s="18"/>
+      <c r="Q943" s="18"/>
+      <c r="R943" s="18"/>
+    </row>
+    <row r="944" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A944" s="45">
+        <v>11</v>
+      </c>
+      <c r="B944" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C944" s="11" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D944" s="11">
+        <v>117032094</v>
+      </c>
+      <c r="E944" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F944" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G944" s="14">
+        <v>4170</v>
+      </c>
+      <c r="H944" s="15">
+        <v>5951</v>
+      </c>
+      <c r="I944" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J944" s="15" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K944" s="18"/>
+      <c r="L944" s="22">
+        <v>71271043</v>
+      </c>
+      <c r="M944" s="18"/>
+      <c r="N944" s="40"/>
+      <c r="O944" s="51"/>
+      <c r="P944" s="18"/>
+      <c r="Q944" s="18"/>
+      <c r="R944" s="18"/>
+    </row>
+    <row r="945" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A945" s="45">
+        <v>12</v>
+      </c>
+      <c r="B945" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C945" s="11" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D945" s="11">
+        <v>124185553</v>
+      </c>
+      <c r="E945" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F945" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G945" s="14">
+        <v>2230</v>
+      </c>
+      <c r="H945" s="15">
+        <v>3342</v>
+      </c>
+      <c r="I945" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J945" s="15" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K945" s="18"/>
+      <c r="L945" s="22">
+        <v>71265800</v>
+      </c>
+      <c r="M945" s="18"/>
+      <c r="N945" s="40"/>
+      <c r="O945" s="51"/>
+      <c r="P945" s="18"/>
+      <c r="Q945" s="18"/>
+      <c r="R945" s="18"/>
+    </row>
+    <row r="946" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A946" s="45">
+        <v>13</v>
+      </c>
+      <c r="B946" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C946" s="11" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D946" s="11">
+        <v>125366206</v>
+      </c>
+      <c r="E946" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F946" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G946" s="14">
+        <v>8626</v>
+      </c>
+      <c r="H946" s="15">
+        <v>682</v>
+      </c>
+      <c r="I946" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J946" s="15" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K946" s="18"/>
+      <c r="L946" s="15" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M946" s="18"/>
+      <c r="N946" s="40"/>
+      <c r="O946" s="51"/>
+      <c r="P946" s="18"/>
+      <c r="Q946" s="18"/>
+      <c r="R946" s="18"/>
+    </row>
+    <row r="947" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A947" s="45">
+        <v>14</v>
+      </c>
+      <c r="B947" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C947" s="11" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D947" s="11">
+        <v>110175741</v>
+      </c>
+      <c r="E947" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F947" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G947" s="14">
+        <v>4750</v>
+      </c>
+      <c r="H947" s="15">
+        <v>1659</v>
+      </c>
+      <c r="I947" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J947" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K947" s="18"/>
+      <c r="L947" s="18"/>
+      <c r="M947" s="18"/>
+      <c r="N947" s="40"/>
+      <c r="O947" s="51"/>
+      <c r="P947" s="18"/>
+      <c r="Q947" s="15">
+        <v>94390585</v>
+      </c>
+      <c r="R947" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="948" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A948" s="45">
+        <v>15</v>
+      </c>
+      <c r="B948" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C948" s="11" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D948" s="11">
+        <v>122236617</v>
+      </c>
+      <c r="E948" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F948" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G948" s="14">
+        <v>6362</v>
+      </c>
+      <c r="H948" s="15">
+        <v>2282</v>
+      </c>
+      <c r="I948" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J948" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="K948" s="18"/>
+      <c r="L948" s="18"/>
+      <c r="M948" s="18"/>
+      <c r="N948" s="40"/>
+      <c r="O948" s="51"/>
+      <c r="P948" s="18"/>
+      <c r="Q948" s="15">
+        <v>96892533051</v>
+      </c>
+      <c r="R948" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="949" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A949" s="45">
+        <v>16</v>
+      </c>
+      <c r="B949" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C949" s="11" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D949" s="11" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E949" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F949" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G949" s="14">
+        <v>56834</v>
+      </c>
+      <c r="H949" s="15">
+        <v>47296</v>
+      </c>
+      <c r="I949" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J949" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K949" s="18"/>
+      <c r="L949" s="18"/>
+      <c r="M949" s="18"/>
+      <c r="N949" s="40"/>
+      <c r="O949" s="51"/>
+      <c r="P949" s="18"/>
+      <c r="Q949" s="18"/>
+      <c r="R949" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="950" spans="1:18" ht="15" thickBot="1">
+      <c r="A950" s="45">
+        <v>17</v>
+      </c>
+      <c r="B950" s="46">
+        <v>46271</v>
+      </c>
+      <c r="C950" s="11" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D950" s="11">
+        <v>118167672</v>
+      </c>
+      <c r="E950" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F950" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G950" s="14">
+        <v>4618</v>
+      </c>
+      <c r="H950" s="15">
+        <v>2186</v>
+      </c>
+      <c r="I950" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J950" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K950" s="18"/>
+      <c r="L950" s="18"/>
+      <c r="M950" s="18"/>
+      <c r="N950" s="40"/>
+      <c r="O950" s="51"/>
+      <c r="P950" s="18"/>
+      <c r="Q950" s="18"/>
+      <c r="R950" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6471007E-51AE-4866-92E0-8CF735FBC434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039E7EEE-F689-4A76-BD1C-5AACBD5DCDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7613" uniqueCount="1630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7942" uniqueCount="1695">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -4711,9 +4711,6 @@
     <t>PORT BLOCKED</t>
   </si>
   <si>
-    <t>CANCEL</t>
-  </si>
-  <si>
     <t>IQBAL MH S</t>
   </si>
   <si>
@@ -4928,6 +4925,204 @@
   </si>
   <si>
     <t>SALIM HAMED</t>
+  </si>
+  <si>
+    <t>SHUJAH BIN</t>
+  </si>
+  <si>
+    <t>AB3590318</t>
+  </si>
+  <si>
+    <t>HABEEB</t>
+  </si>
+  <si>
+    <t>MUHAMMAD SHAFIQUE</t>
+  </si>
+  <si>
+    <t>C/o bilal</t>
+  </si>
+  <si>
+    <t>IKIRAM LATIF</t>
+  </si>
+  <si>
+    <t>CE8481803</t>
+  </si>
+  <si>
+    <t>AP0887532</t>
+  </si>
+  <si>
+    <t>84879*</t>
+  </si>
+  <si>
+    <t>SHAFIQ KHAN</t>
+  </si>
+  <si>
+    <t>SHER WALI KHAN</t>
+  </si>
+  <si>
+    <t>TASEER RAHMAN</t>
+  </si>
+  <si>
+    <t>MAZIN MASOUD</t>
+  </si>
+  <si>
+    <t>MAHMOOD YAQOUB</t>
+  </si>
+  <si>
+    <t>AHMAD MUHAMMAD</t>
+  </si>
+  <si>
+    <t>PR1178052</t>
+  </si>
+  <si>
+    <t>ALI ASGHAR</t>
+  </si>
+  <si>
+    <t>AWAIS UR REHMAN</t>
+  </si>
+  <si>
+    <t>MK5140557</t>
+  </si>
+  <si>
+    <t>BAIG IRFAN</t>
+  </si>
+  <si>
+    <t>AA3926967</t>
+  </si>
+  <si>
+    <t>NAWAZ MUHAMMAD</t>
+  </si>
+  <si>
+    <t>CM9613955</t>
+  </si>
+  <si>
+    <t>IZMAM ATTA</t>
+  </si>
+  <si>
+    <t>AHMAD ALMOHAMAD</t>
+  </si>
+  <si>
+    <t>N014889877</t>
+  </si>
+  <si>
+    <t>MAHMOOD RASHID</t>
+  </si>
+  <si>
+    <t>HF0154283</t>
+  </si>
+  <si>
+    <t>USMAN MUHAMMAD</t>
+  </si>
+  <si>
+    <t>CF2852803</t>
+  </si>
+  <si>
+    <t>AKHTAR NAEEM</t>
+  </si>
+  <si>
+    <t>GQ1347645</t>
+  </si>
+  <si>
+    <t>AZAD SOHAIL</t>
+  </si>
+  <si>
+    <t>AH1877173</t>
+  </si>
+  <si>
+    <t>SADIQ AZIZ UR REHMAN</t>
+  </si>
+  <si>
+    <t>R-GEN/MUSHTAQ</t>
+  </si>
+  <si>
+    <t>RIZWAN</t>
+  </si>
+  <si>
+    <t>AFZAL KHAN</t>
+  </si>
+  <si>
+    <t>9294 9342</t>
+  </si>
+  <si>
+    <t>NAVEEDUL HASSAN</t>
+  </si>
+  <si>
+    <t>R-GEN/SAEED</t>
+  </si>
+  <si>
+    <t>ZAHEER AHMED</t>
+  </si>
+  <si>
+    <t>EY1154505</t>
+  </si>
+  <si>
+    <t>ABID ALI</t>
+  </si>
+  <si>
+    <t>4550*</t>
+  </si>
+  <si>
+    <t>ZAHID IMRAN</t>
+  </si>
+  <si>
+    <t>AMAN ULLAH</t>
+  </si>
+  <si>
+    <t>AZHAR NAWAZ</t>
+  </si>
+  <si>
+    <t>FAIZ AHMED</t>
+  </si>
+  <si>
+    <t>IRFAN ALI</t>
+  </si>
+  <si>
+    <t>JJ1790605</t>
+  </si>
+  <si>
+    <t>R-GEN/IRFAN</t>
+  </si>
+  <si>
+    <t>ZEESHAN</t>
+  </si>
+  <si>
+    <t>R/HAMOOD SULAIMAN</t>
+  </si>
+  <si>
+    <t>ASAD SAID</t>
+  </si>
+  <si>
+    <t>KHALID MOHAMMAD</t>
+  </si>
+  <si>
+    <t>HAMED ALI OMAR</t>
+  </si>
+  <si>
+    <t>HABIB</t>
+  </si>
+  <si>
+    <t>BV6038662</t>
+  </si>
+  <si>
+    <t>LOVE PREET</t>
+  </si>
+  <si>
+    <t>X5439661</t>
+  </si>
+  <si>
+    <t>AMANAT ALI</t>
+  </si>
+  <si>
+    <t>JK1805984</t>
+  </si>
+  <si>
+    <t>SAJJAD HAIDER</t>
+  </si>
+  <si>
+    <t>JUNAID ALI</t>
+  </si>
+  <si>
+    <t>ABRAR YOUNUS</t>
   </si>
 </sst>
 </file>
@@ -5308,7 +5503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5594,6 +5789,45 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5909,7 +6143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:R1047"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -15015,8 +15249,8 @@
       <c r="J200" s="15" t="s">
         <v>774</v>
       </c>
-      <c r="K200" s="17" t="s">
-        <v>12</v>
+      <c r="K200" s="29" t="s">
+        <v>1555</v>
       </c>
       <c r="L200" s="18"/>
       <c r="M200" s="18"/>
@@ -29579,48 +29813,44 @@
       </c>
     </row>
     <row r="526" spans="1:18" ht="28.2" thickBot="1">
-      <c r="A526" s="2">
+      <c r="A526" s="96">
         <v>223</v>
       </c>
-      <c r="B526" s="10">
+      <c r="B526" s="97">
         <v>46267</v>
       </c>
-      <c r="C526" s="11" t="s">
+      <c r="C526" s="98" t="s">
         <v>974</v>
       </c>
-      <c r="D526" s="11" t="s">
+      <c r="D526" s="98" t="s">
         <v>975</v>
       </c>
-      <c r="E526" s="32" t="s">
+      <c r="E526" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="F526" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G526" s="14">
+      <c r="F526" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G526" s="101">
         <v>18552</v>
       </c>
-      <c r="H526" s="15">
+      <c r="H526" s="102">
         <v>36476</v>
       </c>
-      <c r="I526" s="16" t="s">
+      <c r="I526" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="J526" s="15" t="s">
+      <c r="J526" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="K526" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="L526" s="18"/>
-      <c r="M526" s="18"/>
-      <c r="N526" s="40"/>
-      <c r="O526" s="51"/>
-      <c r="P526" s="94" t="s">
-        <v>1557</v>
-      </c>
-      <c r="Q526" s="18"/>
-      <c r="R526" s="20" t="s">
+      <c r="K526" s="104"/>
+      <c r="L526" s="105"/>
+      <c r="M526" s="105"/>
+      <c r="N526" s="105"/>
+      <c r="O526" s="105"/>
+      <c r="P526" s="94"/>
+      <c r="Q526" s="105"/>
+      <c r="R526" s="106" t="s">
         <v>14</v>
       </c>
     </row>
@@ -30895,8 +31125,8 @@
       <c r="J554" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K554" s="17" t="s">
-        <v>12</v>
+      <c r="K554" s="29" t="s">
+        <v>1555</v>
       </c>
       <c r="L554" s="18"/>
       <c r="M554" s="18"/>
@@ -46245,7 +46475,7 @@
         <v>10</v>
       </c>
       <c r="J895" s="15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="K895" s="17" t="s">
         <v>12</v>
@@ -46291,7 +46521,7 @@
         <v>10</v>
       </c>
       <c r="J896" s="15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="K896" s="17" t="s">
         <v>12</v>
@@ -46337,7 +46567,7 @@
         <v>10</v>
       </c>
       <c r="J897" s="15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="K897" s="17" t="s">
         <v>12</v>
@@ -46383,7 +46613,7 @@
         <v>10</v>
       </c>
       <c r="J898" s="15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="K898" s="17" t="s">
         <v>12</v>
@@ -48542,7 +48772,7 @@
         <v>46271</v>
       </c>
       <c r="C946" s="11" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D946" s="11">
         <v>121628418</v>
@@ -48574,7 +48804,7 @@
       <c r="O946" s="51"/>
       <c r="P946" s="18"/>
       <c r="Q946" s="44" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="R946" s="21" t="s">
         <v>56</v>
@@ -48588,7 +48818,7 @@
         <v>46271</v>
       </c>
       <c r="C947" s="11" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D947" s="11">
         <v>13495269</v>
@@ -48600,7 +48830,7 @@
         <v>52</v>
       </c>
       <c r="G947" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H947" s="15">
         <v>3835</v>
@@ -48634,10 +48864,10 @@
         <v>46271</v>
       </c>
       <c r="C948" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D948" s="11" t="s">
         <v>1563</v>
-      </c>
-      <c r="D948" s="11" t="s">
-        <v>1564</v>
       </c>
       <c r="E948" s="12" t="s">
         <v>19</v>
@@ -48678,10 +48908,10 @@
         <v>46271</v>
       </c>
       <c r="C949" s="11" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D949" s="11" t="s">
         <v>1565</v>
-      </c>
-      <c r="D949" s="11" t="s">
-        <v>1566</v>
       </c>
       <c r="E949" s="12" t="s">
         <v>19</v>
@@ -48727,7 +48957,7 @@
         <v>110</v>
       </c>
       <c r="D950" s="11" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="E950" s="12" t="s">
         <v>19</v>
@@ -48770,10 +49000,10 @@
         <v>46271</v>
       </c>
       <c r="C951" s="11" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D951" s="11" t="s">
         <v>1568</v>
-      </c>
-      <c r="D951" s="11" t="s">
-        <v>1569</v>
       </c>
       <c r="E951" s="12" t="s">
         <v>19</v>
@@ -48816,7 +49046,7 @@
         <v>46271</v>
       </c>
       <c r="C952" s="11" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D952" s="11">
         <v>95181219</v>
@@ -48860,10 +49090,10 @@
         <v>46271</v>
       </c>
       <c r="C953" s="11" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D953" s="11" t="s">
         <v>1571</v>
-      </c>
-      <c r="D953" s="11" t="s">
-        <v>1572</v>
       </c>
       <c r="E953" s="12" t="s">
         <v>19</v>
@@ -48904,10 +49134,10 @@
         <v>46271</v>
       </c>
       <c r="C954" s="11" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D954" s="11" t="s">
         <v>1573</v>
-      </c>
-      <c r="D954" s="11" t="s">
-        <v>1574</v>
       </c>
       <c r="E954" s="27" t="s">
         <v>50</v>
@@ -48948,10 +49178,10 @@
         <v>46271</v>
       </c>
       <c r="C955" s="11" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D955" s="11" t="s">
         <v>1575</v>
-      </c>
-      <c r="D955" s="11" t="s">
-        <v>1576</v>
       </c>
       <c r="E955" s="27" t="s">
         <v>50</v>
@@ -48992,7 +49222,7 @@
         <v>46271</v>
       </c>
       <c r="C956" s="11" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D956" s="11">
         <v>74215821</v>
@@ -49036,7 +49266,7 @@
         <v>46271</v>
       </c>
       <c r="C957" s="11" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D957" s="11">
         <v>111632104</v>
@@ -49080,10 +49310,10 @@
         <v>46271</v>
       </c>
       <c r="C958" s="11" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D958" s="11" t="s">
         <v>1579</v>
-      </c>
-      <c r="D958" s="11" t="s">
-        <v>1580</v>
       </c>
       <c r="E958" s="12" t="s">
         <v>19</v>
@@ -49124,10 +49354,10 @@
         <v>46271</v>
       </c>
       <c r="C959" s="11" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D959" s="11" t="s">
         <v>1581</v>
-      </c>
-      <c r="D959" s="11" t="s">
-        <v>1582</v>
       </c>
       <c r="E959" s="12" t="s">
         <v>19</v>
@@ -49170,7 +49400,7 @@
         <v>46271</v>
       </c>
       <c r="C960" s="11" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D960" s="11">
         <v>109926354</v>
@@ -49219,7 +49449,7 @@
         <v>1031</v>
       </c>
       <c r="D961" s="11" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="E961" s="12" t="s">
         <v>19</v>
@@ -49262,10 +49492,10 @@
         <v>46271</v>
       </c>
       <c r="C962" s="11" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D962" s="11" t="s">
         <v>1585</v>
-      </c>
-      <c r="D962" s="11" t="s">
-        <v>1586</v>
       </c>
       <c r="E962" s="12" t="s">
         <v>19</v>
@@ -49306,10 +49536,10 @@
         <v>46271</v>
       </c>
       <c r="C963" s="11" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D963" s="11" t="s">
         <v>1587</v>
-      </c>
-      <c r="D963" s="11" t="s">
-        <v>1588</v>
       </c>
       <c r="E963" s="12" t="s">
         <v>19</v>
@@ -49350,10 +49580,10 @@
         <v>46271</v>
       </c>
       <c r="C964" s="11" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D964" s="11" t="s">
         <v>1589</v>
-      </c>
-      <c r="D964" s="11" t="s">
-        <v>1590</v>
       </c>
       <c r="E964" s="12" t="s">
         <v>19</v>
@@ -49394,10 +49624,10 @@
         <v>46271</v>
       </c>
       <c r="C965" s="11" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D965" s="11" t="s">
         <v>1591</v>
-      </c>
-      <c r="D965" s="11" t="s">
-        <v>1592</v>
       </c>
       <c r="E965" s="26" t="s">
         <v>49</v>
@@ -49440,10 +49670,10 @@
         <v>46271</v>
       </c>
       <c r="C966" s="11" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D966" s="11" t="s">
         <v>1593</v>
-      </c>
-      <c r="D966" s="11" t="s">
-        <v>1594</v>
       </c>
       <c r="E966" s="26" t="s">
         <v>49</v>
@@ -49486,10 +49716,10 @@
         <v>46271</v>
       </c>
       <c r="C967" s="11" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D967" s="11" t="s">
         <v>1595</v>
-      </c>
-      <c r="D967" s="11" t="s">
-        <v>1596</v>
       </c>
       <c r="E967" s="26" t="s">
         <v>49</v>
@@ -49532,10 +49762,10 @@
         <v>46271</v>
       </c>
       <c r="C968" s="11" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D968" s="11" t="s">
         <v>1597</v>
-      </c>
-      <c r="D968" s="11" t="s">
-        <v>1598</v>
       </c>
       <c r="E968" s="26" t="s">
         <v>49</v>
@@ -49578,10 +49808,10 @@
         <v>46271</v>
       </c>
       <c r="C969" s="11" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D969" s="11" t="s">
         <v>1599</v>
-      </c>
-      <c r="D969" s="11" t="s">
-        <v>1600</v>
       </c>
       <c r="E969" s="12" t="s">
         <v>19</v>
@@ -49624,7 +49854,7 @@
         <v>46271</v>
       </c>
       <c r="C970" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="D970" s="11">
         <v>136970853</v>
@@ -49668,7 +49898,7 @@
         <v>46271</v>
       </c>
       <c r="C971" s="11" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="D971" s="11">
         <v>71400641</v>
@@ -49689,7 +49919,7 @@
         <v>53</v>
       </c>
       <c r="J971" s="15" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="K971" s="17" t="s">
         <v>12</v>
@@ -49714,7 +49944,7 @@
         <v>46271</v>
       </c>
       <c r="C972" s="11" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="D972" s="11">
         <v>89287977</v>
@@ -49735,7 +49965,7 @@
         <v>53</v>
       </c>
       <c r="J972" s="15" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="K972" s="17" t="s">
         <v>12</v>
@@ -49760,7 +49990,7 @@
         <v>46271</v>
       </c>
       <c r="C973" s="11" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D973" s="11">
         <v>89086437</v>
@@ -49806,7 +50036,7 @@
         <v>46271</v>
       </c>
       <c r="C974" s="11" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="D974" s="11">
         <v>105851535</v>
@@ -49852,7 +50082,7 @@
         <v>46271</v>
       </c>
       <c r="C975" s="11" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D975" s="11">
         <v>84721616</v>
@@ -50078,10 +50308,10 @@
         <v>46271</v>
       </c>
       <c r="C980" s="11" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D980" s="11" t="s">
         <v>1608</v>
-      </c>
-      <c r="D980" s="11" t="s">
-        <v>1609</v>
       </c>
       <c r="E980" s="26" t="s">
         <v>49</v>
@@ -50122,7 +50352,7 @@
         <v>46271</v>
       </c>
       <c r="C981" s="11" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D981" s="11">
         <v>97214384</v>
@@ -50168,7 +50398,7 @@
         <v>46271</v>
       </c>
       <c r="C982" s="11" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D982" s="11">
         <v>120247757</v>
@@ -50212,7 +50442,7 @@
         <v>46271</v>
       </c>
       <c r="C983" s="11" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D983" s="11">
         <v>86150759</v>
@@ -50224,7 +50454,7 @@
         <v>52</v>
       </c>
       <c r="G983" s="14" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H983" s="15">
         <v>7011</v>
@@ -50277,7 +50507,7 @@
         <v>10</v>
       </c>
       <c r="J984" s="15" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="K984" s="17" t="s">
         <v>12</v>
@@ -50394,7 +50624,7 @@
         <v>46271</v>
       </c>
       <c r="C987" s="11" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D987" s="11">
         <v>127710132</v>
@@ -50443,7 +50673,7 @@
         <v>1277</v>
       </c>
       <c r="D988" s="11" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="E988" s="12" t="s">
         <v>19</v>
@@ -50461,7 +50691,7 @@
         <v>10</v>
       </c>
       <c r="J988" s="15" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="K988" s="17" t="s">
         <v>12</v>
@@ -50486,10 +50716,10 @@
         <v>46271</v>
       </c>
       <c r="C989" s="11" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D989" s="11" t="s">
         <v>1617</v>
-      </c>
-      <c r="D989" s="11" t="s">
-        <v>1618</v>
       </c>
       <c r="E989" s="12" t="s">
         <v>19</v>
@@ -50530,7 +50760,7 @@
         <v>46271</v>
       </c>
       <c r="C990" s="11" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D990" s="11">
         <v>15679714</v>
@@ -50574,7 +50804,7 @@
         <v>46271</v>
       </c>
       <c r="C991" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D991" s="11">
         <v>18280548</v>
@@ -50618,10 +50848,10 @@
         <v>46271</v>
       </c>
       <c r="C992" s="11" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D992" s="11" t="s">
         <v>1621</v>
-      </c>
-      <c r="D992" s="11" t="s">
-        <v>1622</v>
       </c>
       <c r="E992" s="12" t="s">
         <v>19</v>
@@ -50639,7 +50869,7 @@
         <v>10</v>
       </c>
       <c r="J992" s="15" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="K992" s="17" t="s">
         <v>12</v>
@@ -50664,10 +50894,10 @@
         <v>46271</v>
       </c>
       <c r="C993" s="11" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D993" s="11" t="s">
         <v>1623</v>
-      </c>
-      <c r="D993" s="11" t="s">
-        <v>1624</v>
       </c>
       <c r="E993" s="26" t="s">
         <v>49</v>
@@ -50708,7 +50938,7 @@
         <v>46271</v>
       </c>
       <c r="C994" s="11" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D994" s="11">
         <v>68793586</v>
@@ -50786,7 +51016,9 @@
       <c r="O995" s="51"/>
       <c r="P995" s="18"/>
       <c r="Q995" s="18"/>
-      <c r="R995" s="18"/>
+      <c r="R995" s="20" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="996" spans="1:18" ht="28.2" thickBot="1">
       <c r="A996" s="2">
@@ -50796,7 +51028,7 @@
         <v>46271</v>
       </c>
       <c r="C996" s="11" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D996" s="11">
         <v>20541516</v>
@@ -50828,7 +51060,9 @@
       <c r="O996" s="51"/>
       <c r="P996" s="18"/>
       <c r="Q996" s="18"/>
-      <c r="R996" s="18"/>
+      <c r="R996" s="20" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="997" spans="1:18" ht="28.2" thickBot="1">
       <c r="A997" s="2">
@@ -50838,7 +51072,7 @@
         <v>46271</v>
       </c>
       <c r="C997" s="11" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D997" s="11">
         <v>8946281</v>
@@ -50870,7 +51104,9 @@
       <c r="O997" s="51"/>
       <c r="P997" s="18"/>
       <c r="Q997" s="18"/>
-      <c r="R997" s="18"/>
+      <c r="R997" s="20" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="998" spans="1:18" ht="28.2" thickBot="1">
       <c r="A998" s="2">
@@ -50912,7 +51148,9 @@
       <c r="O998" s="51"/>
       <c r="P998" s="18"/>
       <c r="Q998" s="18"/>
-      <c r="R998" s="18"/>
+      <c r="R998" s="20" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="999" spans="1:18" ht="28.2" thickBot="1">
       <c r="A999" s="2">
@@ -50922,7 +51160,7 @@
         <v>46271</v>
       </c>
       <c r="C999" s="11" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D999" s="11">
         <v>7193813</v>
@@ -50954,7 +51192,9 @@
       <c r="O999" s="51"/>
       <c r="P999" s="18"/>
       <c r="Q999" s="18"/>
-      <c r="R999" s="18"/>
+      <c r="R999" s="20" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="1000" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1000" s="2">
@@ -50964,7 +51204,7 @@
         <v>46271</v>
       </c>
       <c r="C1000" s="11" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D1000" s="11">
         <v>3617736</v>
@@ -50996,7 +51236,2023 @@
       <c r="O1000" s="51"/>
       <c r="P1000" s="18"/>
       <c r="Q1000" s="18"/>
-      <c r="R1000" s="18"/>
+      <c r="R1000" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:18" ht="15" thickBot="1">
+      <c r="A1001" s="2">
+        <v>69</v>
+      </c>
+      <c r="B1001" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1001" s="11" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D1001" s="11" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E1001" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1001" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1001" s="14">
+        <v>41870</v>
+      </c>
+      <c r="H1001" s="15">
+        <v>83631</v>
+      </c>
+      <c r="I1001" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1001" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="K1001" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1001" s="18"/>
+      <c r="M1001" s="18"/>
+      <c r="N1001" s="40"/>
+      <c r="O1001" s="51"/>
+      <c r="P1001" s="18"/>
+      <c r="Q1001" s="15">
+        <v>77438127</v>
+      </c>
+      <c r="R1001" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1002" s="2">
+        <v>70</v>
+      </c>
+      <c r="B1002" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1002" s="11" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D1002" s="11">
+        <v>65919668</v>
+      </c>
+      <c r="E1002" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1002" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1002" s="14">
+        <v>8319</v>
+      </c>
+      <c r="H1002" s="15">
+        <v>2816</v>
+      </c>
+      <c r="I1002" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1002" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1002" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1002" s="18"/>
+      <c r="M1002" s="18"/>
+      <c r="N1002" s="40"/>
+      <c r="O1002" s="51"/>
+      <c r="P1002" s="28" t="s">
+        <v>1633</v>
+      </c>
+      <c r="Q1002" s="15">
+        <v>94421839</v>
+      </c>
+      <c r="R1002" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:18" ht="15" thickBot="1">
+      <c r="A1003" s="2">
+        <v>71</v>
+      </c>
+      <c r="B1003" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1003" s="11" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D1003" s="11" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1003" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1003" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1003" s="14">
+        <v>65119</v>
+      </c>
+      <c r="H1003" s="15">
+        <v>84879</v>
+      </c>
+      <c r="I1003" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1003" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1003" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1003" s="18"/>
+      <c r="M1003" s="18"/>
+      <c r="N1003" s="40"/>
+      <c r="O1003" s="51"/>
+      <c r="P1003" s="18"/>
+      <c r="Q1003" s="15">
+        <v>95725624</v>
+      </c>
+      <c r="R1003" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:18" ht="23.4" thickBot="1">
+      <c r="A1004" s="2">
+        <v>72</v>
+      </c>
+      <c r="B1004" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1004" s="11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D1004" s="11" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E1004" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1004" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1004" s="14">
+        <v>48614</v>
+      </c>
+      <c r="H1004" s="15" t="s">
+        <v>1637</v>
+      </c>
+      <c r="I1004" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1004" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1004" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1004" s="18"/>
+      <c r="M1004" s="18"/>
+      <c r="N1004" s="40"/>
+      <c r="O1004" s="51"/>
+      <c r="P1004" s="18"/>
+      <c r="Q1004" s="15">
+        <v>95703477</v>
+      </c>
+      <c r="R1004" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:18" ht="15" thickBot="1">
+      <c r="A1005" s="2">
+        <v>73</v>
+      </c>
+      <c r="B1005" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1005" s="11" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D1005" s="11">
+        <v>121436929</v>
+      </c>
+      <c r="E1005" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1005" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1005" s="14">
+        <v>227</v>
+      </c>
+      <c r="H1005" s="15">
+        <v>7508</v>
+      </c>
+      <c r="I1005" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1005" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K1005" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1005" s="18"/>
+      <c r="M1005" s="18"/>
+      <c r="N1005" s="40"/>
+      <c r="O1005" s="51"/>
+      <c r="P1005" s="18"/>
+      <c r="Q1005" s="15">
+        <v>72533500</v>
+      </c>
+      <c r="R1005" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:18" ht="15" thickBot="1">
+      <c r="A1006" s="2">
+        <v>74</v>
+      </c>
+      <c r="B1006" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1006" s="11" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1006" s="11">
+        <v>134164723</v>
+      </c>
+      <c r="E1006" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1006" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1006" s="14">
+        <v>536</v>
+      </c>
+      <c r="H1006" s="15">
+        <v>1361</v>
+      </c>
+      <c r="I1006" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1006" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K1006" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1006" s="18"/>
+      <c r="M1006" s="18"/>
+      <c r="N1006" s="40"/>
+      <c r="O1006" s="51"/>
+      <c r="P1006" s="18"/>
+      <c r="Q1006" s="15">
+        <v>95809120</v>
+      </c>
+      <c r="R1006" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:18" ht="15" thickBot="1">
+      <c r="A1007" s="2">
+        <v>75</v>
+      </c>
+      <c r="B1007" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1007" s="11" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D1007" s="11">
+        <v>118004559</v>
+      </c>
+      <c r="E1007" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1007" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1007" s="14">
+        <v>4364</v>
+      </c>
+      <c r="H1007" s="15">
+        <v>9036</v>
+      </c>
+      <c r="I1007" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1007" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K1007" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1007" s="18"/>
+      <c r="M1007" s="18"/>
+      <c r="N1007" s="40"/>
+      <c r="O1007" s="51"/>
+      <c r="P1007" s="18"/>
+      <c r="Q1007" s="15">
+        <v>76920926</v>
+      </c>
+      <c r="R1007" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1008" s="2">
+        <v>76</v>
+      </c>
+      <c r="B1008" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1008" s="11" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D1008" s="11">
+        <v>14689538</v>
+      </c>
+      <c r="E1008" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1008" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1008" s="14">
+        <v>6807</v>
+      </c>
+      <c r="H1008" s="15">
+        <v>8440</v>
+      </c>
+      <c r="I1008" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1008" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="K1008" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1008" s="18"/>
+      <c r="M1008" s="18"/>
+      <c r="N1008" s="40"/>
+      <c r="O1008" s="51"/>
+      <c r="P1008" s="18"/>
+      <c r="Q1008" s="18"/>
+      <c r="R1008" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1009" s="2">
+        <v>77</v>
+      </c>
+      <c r="B1009" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1009" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="D1009" s="11">
+        <v>12889072</v>
+      </c>
+      <c r="E1009" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1009" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1009" s="14">
+        <v>1644</v>
+      </c>
+      <c r="H1009" s="15">
+        <v>9273</v>
+      </c>
+      <c r="I1009" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1009" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="K1009" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1009" s="18"/>
+      <c r="M1009" s="18"/>
+      <c r="N1009" s="40"/>
+      <c r="O1009" s="51"/>
+      <c r="P1009" s="18"/>
+      <c r="Q1009" s="18"/>
+      <c r="R1009" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1010" s="2">
+        <v>78</v>
+      </c>
+      <c r="B1010" s="10">
+        <v>46271</v>
+      </c>
+      <c r="C1010" s="11" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D1010" s="11">
+        <v>20601901</v>
+      </c>
+      <c r="E1010" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1010" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1010" s="14">
+        <v>6019</v>
+      </c>
+      <c r="H1010" s="15">
+        <v>9696</v>
+      </c>
+      <c r="I1010" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1010" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="K1010" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1010" s="18"/>
+      <c r="M1010" s="18"/>
+      <c r="N1010" s="40"/>
+      <c r="O1010" s="51"/>
+      <c r="P1010" s="18"/>
+      <c r="Q1010" s="18"/>
+      <c r="R1010" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:18" ht="15" thickBot="1">
+      <c r="A1011" s="72">
+        <v>1</v>
+      </c>
+      <c r="B1011" s="73">
+        <v>46272</v>
+      </c>
+      <c r="C1011" s="74" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D1011" s="74" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E1011" s="107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1011" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1011" s="77">
+        <v>93531</v>
+      </c>
+      <c r="H1011" s="78">
+        <v>96449</v>
+      </c>
+      <c r="I1011" s="79" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1011" s="78" t="s">
+        <v>1613</v>
+      </c>
+      <c r="K1011" s="81"/>
+      <c r="L1011" s="81"/>
+      <c r="M1011" s="81"/>
+      <c r="N1011" s="81"/>
+      <c r="O1011" s="81"/>
+      <c r="P1011" s="81"/>
+      <c r="Q1011" s="78">
+        <v>96054576</v>
+      </c>
+      <c r="R1011" s="82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1012" s="2">
+        <v>2</v>
+      </c>
+      <c r="B1012" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1012" s="11" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D1012" s="11">
+        <v>68895681</v>
+      </c>
+      <c r="E1012" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1012" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1012" s="14">
+        <v>8558</v>
+      </c>
+      <c r="H1012" s="15">
+        <v>9022</v>
+      </c>
+      <c r="I1012" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1012" s="15" t="s">
+        <v>906</v>
+      </c>
+      <c r="K1012" s="18"/>
+      <c r="L1012" s="18"/>
+      <c r="M1012" s="18"/>
+      <c r="N1012" s="40"/>
+      <c r="O1012" s="51"/>
+      <c r="P1012" s="18"/>
+      <c r="Q1012" s="15">
+        <v>94232210</v>
+      </c>
+      <c r="R1012" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:18" ht="15" thickBot="1">
+      <c r="A1013" s="108"/>
+      <c r="B1013" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1013" s="11" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D1013" s="11">
+        <v>102839029</v>
+      </c>
+      <c r="E1013" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1013" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1013" s="14">
+        <v>6146</v>
+      </c>
+      <c r="H1013" s="15">
+        <v>922</v>
+      </c>
+      <c r="I1013" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1013" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1013" s="18"/>
+      <c r="L1013" s="18"/>
+      <c r="M1013" s="18"/>
+      <c r="N1013" s="40"/>
+      <c r="O1013" s="51"/>
+      <c r="P1013" s="18"/>
+      <c r="Q1013" s="15">
+        <v>96879684447</v>
+      </c>
+      <c r="R1013" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:18" ht="15" thickBot="1">
+      <c r="A1014" s="108"/>
+      <c r="B1014" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1014" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1014" s="11">
+        <v>135417591</v>
+      </c>
+      <c r="E1014" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1014" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1014" s="14">
+        <v>1298</v>
+      </c>
+      <c r="H1014" s="15">
+        <v>3671</v>
+      </c>
+      <c r="I1014" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1014" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1014" s="18"/>
+      <c r="L1014" s="18"/>
+      <c r="M1014" s="18"/>
+      <c r="N1014" s="40"/>
+      <c r="O1014" s="51"/>
+      <c r="P1014" s="18"/>
+      <c r="Q1014" s="15">
+        <v>96871007871</v>
+      </c>
+      <c r="R1014" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:18" ht="15" thickBot="1">
+      <c r="A1015" s="108"/>
+      <c r="B1015" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1015" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D1015" s="11" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E1015" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1015" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1015" s="14">
+        <v>56846</v>
+      </c>
+      <c r="H1015" s="18"/>
+      <c r="I1015" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1015" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K1015" s="18"/>
+      <c r="L1015" s="18"/>
+      <c r="M1015" s="18"/>
+      <c r="N1015" s="40"/>
+      <c r="O1015" s="51"/>
+      <c r="P1015" s="18"/>
+      <c r="Q1015" s="15">
+        <v>70204740</v>
+      </c>
+      <c r="R1015" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:18" ht="15" thickBot="1">
+      <c r="A1016" s="108"/>
+      <c r="B1016" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1016" s="11" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D1016" s="11" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E1016" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1016" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1016" s="14">
+        <v>20400</v>
+      </c>
+      <c r="H1016" s="15">
+        <v>40422</v>
+      </c>
+      <c r="I1016" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1016" s="15" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K1016" s="18"/>
+      <c r="L1016" s="18"/>
+      <c r="M1016" s="18"/>
+      <c r="N1016" s="40"/>
+      <c r="O1016" s="51"/>
+      <c r="P1016" s="18"/>
+      <c r="Q1016" s="15">
+        <v>94210084</v>
+      </c>
+      <c r="R1016" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:18" ht="15" thickBot="1">
+      <c r="A1017" s="108"/>
+      <c r="B1017" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1017" s="11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D1017" s="11">
+        <v>97688908</v>
+      </c>
+      <c r="E1017" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1017" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1017" s="14">
+        <v>8134</v>
+      </c>
+      <c r="H1017" s="15">
+        <v>-4870</v>
+      </c>
+      <c r="I1017" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1017" s="15" t="s">
+        <v>1613</v>
+      </c>
+      <c r="K1017" s="18"/>
+      <c r="L1017" s="18"/>
+      <c r="M1017" s="18"/>
+      <c r="N1017" s="40"/>
+      <c r="O1017" s="51"/>
+      <c r="P1017" s="18"/>
+      <c r="Q1017" s="15">
+        <v>92776061</v>
+      </c>
+      <c r="R1017" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:18" ht="15" thickBot="1">
+      <c r="A1018" s="108"/>
+      <c r="B1018" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1018" s="11" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D1018" s="11" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E1018" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1018" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1018" s="14">
+        <v>48267</v>
+      </c>
+      <c r="H1018" s="15">
+        <v>37452</v>
+      </c>
+      <c r="I1018" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1018" s="15" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K1018" s="18"/>
+      <c r="L1018" s="18"/>
+      <c r="M1018" s="18"/>
+      <c r="N1018" s="40"/>
+      <c r="O1018" s="51"/>
+      <c r="P1018" s="18"/>
+      <c r="Q1018" s="15">
+        <v>95879335</v>
+      </c>
+      <c r="R1018" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:18" ht="15" thickBot="1">
+      <c r="A1019" s="108"/>
+      <c r="B1019" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1019" s="11" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D1019" s="11">
+        <v>72430246</v>
+      </c>
+      <c r="E1019" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1019" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1019" s="14">
+        <v>5580</v>
+      </c>
+      <c r="H1019" s="15">
+        <v>-5851</v>
+      </c>
+      <c r="I1019" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1019" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1019" s="18"/>
+      <c r="L1019" s="18"/>
+      <c r="M1019" s="18"/>
+      <c r="N1019" s="40"/>
+      <c r="O1019" s="51"/>
+      <c r="P1019" s="18"/>
+      <c r="Q1019" s="18"/>
+      <c r="R1019" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1020" s="108"/>
+      <c r="B1020" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1020" s="11" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D1020" s="11" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E1020" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1020" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1020" s="14">
+        <v>82203</v>
+      </c>
+      <c r="H1020" s="18"/>
+      <c r="I1020" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1020" s="15" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K1020" s="18"/>
+      <c r="L1020" s="18"/>
+      <c r="M1020" s="18"/>
+      <c r="N1020" s="40"/>
+      <c r="O1020" s="51"/>
+      <c r="P1020" s="18"/>
+      <c r="Q1020" s="18"/>
+      <c r="R1020" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:18" ht="15" thickBot="1">
+      <c r="A1021" s="108"/>
+      <c r="B1021" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1021" s="11" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D1021" s="11" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E1021" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1021" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1021" s="14">
+        <v>37285</v>
+      </c>
+      <c r="H1021" s="15">
+        <v>56579</v>
+      </c>
+      <c r="I1021" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1021" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="K1021" s="18"/>
+      <c r="L1021" s="18"/>
+      <c r="M1021" s="18"/>
+      <c r="N1021" s="40"/>
+      <c r="O1021" s="51"/>
+      <c r="P1021" s="18"/>
+      <c r="Q1021" s="15">
+        <v>95697183</v>
+      </c>
+      <c r="R1021" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:18" ht="15" thickBot="1">
+      <c r="A1022" s="108"/>
+      <c r="B1022" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1022" s="11" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D1022" s="11" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E1022" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1022" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1022" s="14">
+        <v>52051</v>
+      </c>
+      <c r="H1022" s="15">
+        <v>21891</v>
+      </c>
+      <c r="I1022" s="18"/>
+      <c r="J1022" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="K1022" s="18"/>
+      <c r="L1022" s="18"/>
+      <c r="M1022" s="18"/>
+      <c r="N1022" s="40"/>
+      <c r="O1022" s="51"/>
+      <c r="P1022" s="18"/>
+      <c r="Q1022" s="15">
+        <v>77415839</v>
+      </c>
+      <c r="R1022" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:18" ht="15" thickBot="1">
+      <c r="A1023" s="108"/>
+      <c r="B1023" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1023" s="11" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D1023" s="11" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E1023" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1023" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1023" s="14">
+        <v>62218</v>
+      </c>
+      <c r="H1023" s="15">
+        <v>47754</v>
+      </c>
+      <c r="I1023" s="18"/>
+      <c r="J1023" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="K1023" s="18"/>
+      <c r="L1023" s="18"/>
+      <c r="M1023" s="18"/>
+      <c r="N1023" s="40"/>
+      <c r="O1023" s="51"/>
+      <c r="P1023" s="18"/>
+      <c r="Q1023" s="18"/>
+      <c r="R1023" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:18" ht="15" thickBot="1">
+      <c r="A1024" s="108"/>
+      <c r="B1024" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1024" s="11" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D1024" s="11" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1024" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1024" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1024" s="14">
+        <v>34288</v>
+      </c>
+      <c r="H1024" s="15">
+        <v>82963</v>
+      </c>
+      <c r="I1024" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1024" s="15" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K1024" s="18"/>
+      <c r="L1024" s="18"/>
+      <c r="M1024" s="18"/>
+      <c r="N1024" s="40"/>
+      <c r="O1024" s="51"/>
+      <c r="P1024" s="18"/>
+      <c r="Q1024" s="38">
+        <v>554202113</v>
+      </c>
+      <c r="R1024" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:18" ht="42" thickBot="1">
+      <c r="A1025" s="108"/>
+      <c r="B1025" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1025" s="11" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D1025" s="11">
+        <v>121883506</v>
+      </c>
+      <c r="E1025" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1025" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1025" s="14">
+        <v>196</v>
+      </c>
+      <c r="H1025" s="15">
+        <v>997</v>
+      </c>
+      <c r="I1025" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1025" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K1025" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1025" s="18"/>
+      <c r="M1025" s="18"/>
+      <c r="N1025" s="40"/>
+      <c r="O1025" s="51"/>
+      <c r="P1025" s="18"/>
+      <c r="Q1025" s="30"/>
+      <c r="R1025" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:18" ht="42" thickBot="1">
+      <c r="A1026" s="108"/>
+      <c r="B1026" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1026" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D1026" s="11">
+        <v>69063047</v>
+      </c>
+      <c r="E1026" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1026" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1026" s="14">
+        <v>9259</v>
+      </c>
+      <c r="H1026" s="15">
+        <v>2242</v>
+      </c>
+      <c r="I1026" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1026" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K1026" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1026" s="18"/>
+      <c r="M1026" s="18"/>
+      <c r="N1026" s="40"/>
+      <c r="O1026" s="51"/>
+      <c r="P1026" s="18"/>
+      <c r="Q1026" s="30"/>
+      <c r="R1026" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1027" s="108"/>
+      <c r="B1027" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1027" s="11" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D1027" s="11">
+        <v>104800768</v>
+      </c>
+      <c r="E1027" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1027" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1027" s="14">
+        <v>8472</v>
+      </c>
+      <c r="H1027" s="15">
+        <v>8481</v>
+      </c>
+      <c r="I1027" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1027" s="15" t="s">
+        <v>1546</v>
+      </c>
+      <c r="K1027" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1027" s="18"/>
+      <c r="M1027" s="18"/>
+      <c r="N1027" s="40"/>
+      <c r="O1027" s="51"/>
+      <c r="P1027" s="18"/>
+      <c r="Q1027" s="38" t="s">
+        <v>1667</v>
+      </c>
+      <c r="R1027" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1028" s="108"/>
+      <c r="B1028" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1028" s="11" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D1028" s="11">
+        <v>102338592</v>
+      </c>
+      <c r="E1028" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1028" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1028" s="14">
+        <v>9183</v>
+      </c>
+      <c r="H1028" s="15">
+        <v>9392</v>
+      </c>
+      <c r="I1028" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1028" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K1028" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1028" s="18"/>
+      <c r="M1028" s="18"/>
+      <c r="N1028" s="40"/>
+      <c r="O1028" s="51"/>
+      <c r="P1028" s="18"/>
+      <c r="Q1028" s="44">
+        <v>99252486</v>
+      </c>
+      <c r="R1028" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1029" s="108"/>
+      <c r="B1029" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1029" s="11" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D1029" s="11" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E1029" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1029" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1029" s="14">
+        <v>63339</v>
+      </c>
+      <c r="H1029" s="15">
+        <v>69919</v>
+      </c>
+      <c r="I1029" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1029" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1029" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1029" s="18"/>
+      <c r="M1029" s="18"/>
+      <c r="N1029" s="40"/>
+      <c r="O1029" s="51"/>
+      <c r="P1029" s="18"/>
+      <c r="Q1029" s="44">
+        <v>95783678</v>
+      </c>
+      <c r="R1029" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1030" s="108"/>
+      <c r="B1030" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1030" s="11" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D1030" s="11">
+        <v>106233417</v>
+      </c>
+      <c r="E1030" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1030" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1030" s="14">
+        <v>312</v>
+      </c>
+      <c r="H1030" s="15" t="s">
+        <v>1673</v>
+      </c>
+      <c r="I1030" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1030" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1030" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1030" s="18"/>
+      <c r="M1030" s="18"/>
+      <c r="N1030" s="40"/>
+      <c r="O1030" s="51"/>
+      <c r="P1030" s="18"/>
+      <c r="Q1030" s="22">
+        <v>92674713</v>
+      </c>
+      <c r="R1030" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1031" s="108"/>
+      <c r="B1031" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1031" s="11" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D1031" s="11">
+        <v>127851887</v>
+      </c>
+      <c r="E1031" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1031" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1031" s="14">
+        <v>8136</v>
+      </c>
+      <c r="H1031" s="15">
+        <v>4671</v>
+      </c>
+      <c r="I1031" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1031" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1031" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1031" s="18"/>
+      <c r="M1031" s="18"/>
+      <c r="N1031" s="40"/>
+      <c r="O1031" s="51"/>
+      <c r="P1031" s="18"/>
+      <c r="Q1031" s="22">
+        <v>79633715</v>
+      </c>
+      <c r="R1031" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1032" s="108"/>
+      <c r="B1032" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1032" s="11" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D1032" s="11">
+        <v>100135215</v>
+      </c>
+      <c r="E1032" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1032" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1032" s="14">
+        <v>4849</v>
+      </c>
+      <c r="H1032" s="15">
+        <v>3655</v>
+      </c>
+      <c r="I1032" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1032" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1032" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1032" s="18"/>
+      <c r="M1032" s="18"/>
+      <c r="N1032" s="40"/>
+      <c r="O1032" s="51"/>
+      <c r="P1032" s="18"/>
+      <c r="Q1032" s="22">
+        <v>95321343</v>
+      </c>
+      <c r="R1032" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1033" s="108"/>
+      <c r="B1033" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1033" s="11" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D1033" s="11">
+        <v>124743013</v>
+      </c>
+      <c r="E1033" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1033" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1033" s="14">
+        <v>2279</v>
+      </c>
+      <c r="H1033" s="15">
+        <v>4697</v>
+      </c>
+      <c r="I1033" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1033" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1033" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1033" s="18"/>
+      <c r="M1033" s="18"/>
+      <c r="N1033" s="40"/>
+      <c r="O1033" s="51"/>
+      <c r="P1033" s="18"/>
+      <c r="Q1033" s="22">
+        <v>98072553</v>
+      </c>
+      <c r="R1033" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1034" s="108"/>
+      <c r="B1034" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1034" s="11" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D1034" s="11">
+        <v>98480688</v>
+      </c>
+      <c r="E1034" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1034" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1034" s="14">
+        <v>425</v>
+      </c>
+      <c r="H1034" s="15">
+        <v>7878</v>
+      </c>
+      <c r="I1034" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1034" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1034" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1034" s="18"/>
+      <c r="M1034" s="18"/>
+      <c r="N1034" s="40"/>
+      <c r="O1034" s="51"/>
+      <c r="P1034" s="18"/>
+      <c r="Q1034" s="22">
+        <v>93974951</v>
+      </c>
+      <c r="R1034" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1035" s="108"/>
+      <c r="B1035" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1035" s="11" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D1035" s="11" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E1035" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1035" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1035" s="14">
+        <v>48738</v>
+      </c>
+      <c r="H1035" s="15">
+        <v>37765</v>
+      </c>
+      <c r="I1035" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1035" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K1035" s="18"/>
+      <c r="L1035" s="22">
+        <v>99869058</v>
+      </c>
+      <c r="M1035" s="18"/>
+      <c r="N1035" s="40"/>
+      <c r="O1035" s="51"/>
+      <c r="P1035" s="18"/>
+      <c r="Q1035" s="30"/>
+      <c r="R1035" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:18" ht="42" thickBot="1">
+      <c r="A1036" s="108"/>
+      <c r="B1036" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1036" s="11" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D1036" s="11">
+        <v>137462763</v>
+      </c>
+      <c r="E1036" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1036" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1036" s="14">
+        <v>7950</v>
+      </c>
+      <c r="H1036" s="15">
+        <v>2196</v>
+      </c>
+      <c r="I1036" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1036" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1036" s="18"/>
+      <c r="L1036" s="15">
+        <v>77165448</v>
+      </c>
+      <c r="M1036" s="18"/>
+      <c r="N1036" s="40"/>
+      <c r="O1036" s="51"/>
+      <c r="P1036" s="18"/>
+      <c r="Q1036" s="30"/>
+      <c r="R1036" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1037" s="108"/>
+      <c r="B1037" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1037" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="D1037" s="11">
+        <v>3816315</v>
+      </c>
+      <c r="E1037" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1037" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1037" s="14">
+        <v>1455</v>
+      </c>
+      <c r="H1037" s="15">
+        <v>9624</v>
+      </c>
+      <c r="I1037" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1037" s="22" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K1037" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L1037" s="18"/>
+      <c r="M1037" s="18"/>
+      <c r="N1037" s="40"/>
+      <c r="O1037" s="51"/>
+      <c r="P1037" s="18"/>
+      <c r="Q1037" s="30"/>
+      <c r="R1037" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1038" s="108"/>
+      <c r="B1038" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1038" s="11" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D1038" s="11">
+        <v>15460451</v>
+      </c>
+      <c r="E1038" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1038" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1038" s="14">
+        <v>8827</v>
+      </c>
+      <c r="H1038" s="15">
+        <v>8366</v>
+      </c>
+      <c r="I1038" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1038" s="22" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K1038" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L1038" s="18"/>
+      <c r="M1038" s="18"/>
+      <c r="N1038" s="40"/>
+      <c r="O1038" s="51"/>
+      <c r="P1038" s="18"/>
+      <c r="Q1038" s="30"/>
+      <c r="R1038" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1039" s="108"/>
+      <c r="B1039" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1039" s="11" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D1039" s="11">
+        <v>11840764</v>
+      </c>
+      <c r="E1039" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1039" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1039" s="14">
+        <v>9084</v>
+      </c>
+      <c r="H1039" s="15">
+        <v>6776</v>
+      </c>
+      <c r="I1039" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1039" s="22" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K1039" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L1039" s="18"/>
+      <c r="M1039" s="18"/>
+      <c r="N1039" s="40"/>
+      <c r="O1039" s="51"/>
+      <c r="P1039" s="18"/>
+      <c r="Q1039" s="30"/>
+      <c r="R1039" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1040" s="108"/>
+      <c r="B1040" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1040" s="11" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D1040" s="11">
+        <v>19227219</v>
+      </c>
+      <c r="E1040" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1040" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1040" s="14">
+        <v>4520</v>
+      </c>
+      <c r="H1040" s="15">
+        <v>3728</v>
+      </c>
+      <c r="I1040" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1040" s="22" t="s">
+        <v>1682</v>
+      </c>
+      <c r="K1040" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="L1040" s="18"/>
+      <c r="M1040" s="18"/>
+      <c r="N1040" s="40"/>
+      <c r="O1040" s="51"/>
+      <c r="P1040" s="18"/>
+      <c r="Q1040" s="30"/>
+      <c r="R1040" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:18" ht="15" thickBot="1">
+      <c r="A1041" s="108"/>
+      <c r="B1041" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1041" s="11" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D1041" s="11" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E1041" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1041" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1041" s="14">
+        <v>60682</v>
+      </c>
+      <c r="H1041" s="15">
+        <v>58589</v>
+      </c>
+      <c r="I1041" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1041" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1041" s="18"/>
+      <c r="L1041" s="18"/>
+      <c r="M1041" s="18"/>
+      <c r="N1041" s="40"/>
+      <c r="O1041" s="51"/>
+      <c r="P1041" s="18"/>
+      <c r="Q1041" s="30"/>
+      <c r="R1041" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:18" ht="15" thickBot="1">
+      <c r="A1042" s="108"/>
+      <c r="B1042" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1042" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1042" s="11">
+        <v>100543586</v>
+      </c>
+      <c r="E1042" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1042" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1042" s="14">
+        <v>2125</v>
+      </c>
+      <c r="H1042" s="15">
+        <v>6443</v>
+      </c>
+      <c r="I1042" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1042" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1042" s="18"/>
+      <c r="L1042" s="18"/>
+      <c r="M1042" s="18"/>
+      <c r="N1042" s="40"/>
+      <c r="O1042" s="51"/>
+      <c r="P1042" s="18"/>
+      <c r="Q1042" s="38">
+        <v>91208796</v>
+      </c>
+      <c r="R1042" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:18" ht="15" thickBot="1">
+      <c r="A1043" s="108"/>
+      <c r="B1043" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1043" s="11" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D1043" s="11" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E1043" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1043" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1043" s="14">
+        <v>42105</v>
+      </c>
+      <c r="H1043" s="15">
+        <v>10677</v>
+      </c>
+      <c r="I1043" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1043" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1043" s="18"/>
+      <c r="L1043" s="18"/>
+      <c r="M1043" s="18"/>
+      <c r="N1043" s="40"/>
+      <c r="O1043" s="51"/>
+      <c r="P1043" s="18"/>
+      <c r="Q1043" s="38">
+        <v>95774314</v>
+      </c>
+      <c r="R1043" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:18" ht="15" thickBot="1">
+      <c r="A1044" s="108"/>
+      <c r="B1044" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1044" s="11" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D1044" s="11" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E1044" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1044" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1044" s="14">
+        <v>80868</v>
+      </c>
+      <c r="H1044" s="15">
+        <v>48495</v>
+      </c>
+      <c r="I1044" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1044" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1044" s="18"/>
+      <c r="L1044" s="18"/>
+      <c r="M1044" s="18"/>
+      <c r="N1044" s="40"/>
+      <c r="O1044" s="51"/>
+      <c r="P1044" s="18"/>
+      <c r="Q1044" s="44">
+        <v>97618752</v>
+      </c>
+      <c r="R1044" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:18" ht="15" thickBot="1">
+      <c r="A1045" s="108"/>
+      <c r="B1045" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1045" s="11" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D1045" s="11">
+        <v>62305079</v>
+      </c>
+      <c r="E1045" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1045" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1045" s="14">
+        <v>2390</v>
+      </c>
+      <c r="H1045" s="15">
+        <v>7951</v>
+      </c>
+      <c r="I1045" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1045" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1045" s="18"/>
+      <c r="L1045" s="18"/>
+      <c r="M1045" s="18"/>
+      <c r="N1045" s="40"/>
+      <c r="O1045" s="51"/>
+      <c r="P1045" s="18"/>
+      <c r="Q1045" s="38">
+        <v>99694736</v>
+      </c>
+      <c r="R1045" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1046" s="108"/>
+      <c r="B1046" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1046" s="11" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D1046" s="11">
+        <v>133513189</v>
+      </c>
+      <c r="E1046" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1046" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1046" s="14">
+        <v>2763</v>
+      </c>
+      <c r="H1046" s="15">
+        <v>9899</v>
+      </c>
+      <c r="I1046" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1046" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="K1046" s="18"/>
+      <c r="L1046" s="18"/>
+      <c r="M1046" s="18"/>
+      <c r="N1046" s="40"/>
+      <c r="O1046" s="51"/>
+      <c r="P1046" s="18"/>
+      <c r="Q1046" s="44">
+        <v>95525617</v>
+      </c>
+      <c r="R1046" s="21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1047" s="108"/>
+      <c r="B1047" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C1047" s="11" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D1047" s="11">
+        <v>126123361</v>
+      </c>
+      <c r="E1047" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1047" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1047" s="14">
+        <v>791</v>
+      </c>
+      <c r="H1047" s="15">
+        <v>2232</v>
+      </c>
+      <c r="I1047" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1047" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="K1047" s="18"/>
+      <c r="L1047" s="18"/>
+      <c r="M1047" s="18"/>
+      <c r="N1047" s="40"/>
+      <c r="O1047" s="51"/>
+      <c r="P1047" s="18"/>
+      <c r="Q1047" s="44">
+        <v>97301625</v>
+      </c>
+      <c r="R1047" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
